--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azs1\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-kk_29knp\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC252264-CC29-4709-B885-00D0045D9536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32655BD-CD7D-411F-B663-FC2D44C9880D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3645" yWindow="-13320" windowWidth="5970" windowHeight="10455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月度总览" sheetId="1" r:id="rId1"/>
@@ -27,36 +27,42 @@
     <sheet name="每日费用" sheetId="12" r:id="rId12"/>
     <sheet name="10月费用预测" sheetId="13" r:id="rId13"/>
     <sheet name="分摊与计价方式" sheetId="14" r:id="rId14"/>
-    <sheet name="建议与跟踪" sheetId="15" r:id="rId15"/>
-    <sheet name="数据库与缓存用量" sheetId="16" r:id="rId16"/>
-    <sheet name="存储容量与层级" sheetId="17" r:id="rId17"/>
-    <sheet name="日志摄取与保留" sheetId="18" r:id="rId18"/>
-    <sheet name="预算检查" sheetId="19" r:id="rId19"/>
-    <sheet name="数据覆盖与说明" sheetId="20" r:id="rId20"/>
+    <sheet name="RI与SP" sheetId="15" r:id="rId15"/>
+    <sheet name="Azure购买建议" sheetId="16" r:id="rId16"/>
+    <sheet name="建议与跟踪" sheetId="17" r:id="rId17"/>
+    <sheet name="数据库与缓存用量" sheetId="18" r:id="rId18"/>
+    <sheet name="存储容量与层级" sheetId="19" r:id="rId19"/>
+    <sheet name="日志摄取与保留" sheetId="20" r:id="rId20"/>
+    <sheet name="预算检查" sheetId="21" r:id="rId21"/>
+    <sheet name="数据覆盖与说明" sheetId="22" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'10月费用预测'!$A$3:$I$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'9月资源费用'!$A$3:$F$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">Azure购买建议!$A$3:$J$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">RI与SP!$A$3:$I$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">业务组对比!$A$3:$H$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">主要计量变化!$A$3:$K$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">分摊与计价方式!$A$3:$C$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">分摊与计价方式!$A$3:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">区域对比!$A$3:$I$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">变化原因拆解!$A$3:$L$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">图表!$A$3:$J$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">增长与下降来源!$A$3:$H$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">存储容量与层级!$A$3:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">建议与跟踪!$A$3:$L$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">数据库与缓存用量!$A$3:$M$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">数据覆盖与说明!$A$3:$B$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">日志摄取与保留!$A$3:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">存储容量与层级!$A$3:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">建议与跟踪!$A$3:$L$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">数据库与缓存用量!$A$3:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">数据覆盖与说明!$A$3:$B$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">日志摄取与保留!$A$3:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月度总览!$A$3:$C$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">服务对比!$A$3:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">每日费用!$A$3:$C$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">订阅对比!$A$3:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">资源组对比!$A$3:$F$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">预算检查!$A$3:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">预算检查!$A$3:$I$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'10月费用预测'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'9月资源费用'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">Azure购买建议!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">RI与SP!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">业务组对比!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">主要计量变化!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">分摊与计价方式!$1:$3</definedName>
@@ -64,17 +70,17 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">变化原因拆解!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">图表!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">增长与下降来源!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">存储容量与层级!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">建议与跟踪!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">数据库与缓存用量!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="19">数据覆盖与说明!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="17">日志摄取与保留!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="18">存储容量与层级!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">建议与跟踪!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="17">数据库与缓存用量!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="21">数据覆盖与说明!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="19">日志摄取与保留!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">月度总览!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">服务对比!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">每日费用!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">订阅对比!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">资源组对比!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="18">预算检查!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="20">预算检查!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -94,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="571">
   <si>
     <t>示例客户：2026年9月成本巡检（对比8月）</t>
   </si>
@@ -168,7 +174,7 @@
     <t>数据查询时间</t>
   </si>
   <si>
-    <t>2026-10-27T02:32:52.730497+00:00</t>
+    <t>2026-10-27T06:11:07.154271+00:00</t>
   </si>
   <si>
     <t>完整月份费用按查询时结果列示</t>
@@ -1143,15 +1149,144 @@
     <t>OnDemand</t>
   </si>
   <si>
+    <t>分摊费用/计价方式（按资源汇总）</t>
+  </si>
+  <si>
+    <t>ondemand</t>
+  </si>
+  <si>
+    <t>reservation</t>
+  </si>
+  <si>
+    <t>现有预留实例（RI）和节省计划（SP）</t>
+  </si>
+  <si>
+    <t>使用率来自 Azure；近 30 天低于 80% 视为未用满，90 天内到期单独提示。读不到订单时不代表没有购买。</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>规格或承诺</t>
+  </si>
+  <si>
+    <t>范围</t>
+  </si>
+  <si>
+    <t>期限</t>
+  </si>
+  <si>
+    <t>近7天使用率%</t>
+  </si>
+  <si>
+    <t>近30天使用率%</t>
+  </si>
+  <si>
+    <t>到期日期</t>
+  </si>
+  <si>
+    <t>提示</t>
+  </si>
+  <si>
+    <t>预留实例</t>
+  </si>
+  <si>
+    <t>shop-web-d4sv5</t>
+  </si>
+  <si>
+    <t>Standard_D4s_v5</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>1 年</t>
+  </si>
+  <si>
+    <t>2027-03-31</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>legacy-report-e16sv5</t>
+  </si>
+  <si>
+    <t>Standard_E16s_v5</t>
+  </si>
+  <si>
+    <t>Shared</t>
+  </si>
+  <si>
+    <t>2027-05-31</t>
+  </si>
+  <si>
+    <t>近 30 天使用率 0%，未用满</t>
+  </si>
+  <si>
+    <t>节省计划</t>
+  </si>
+  <si>
+    <t>compute-sp-2025</t>
+  </si>
+  <si>
+    <t>每小时承诺 USD 1.20</t>
+  </si>
+  <si>
+    <t>2026-12-15</t>
+  </si>
+  <si>
+    <t>49 天后到期，未设置自动续订</t>
+  </si>
+  <si>
+    <t>Azure 基于过去 30 天用量的 RI/SP 购买建议</t>
+  </si>
+  <si>
+    <t>金额为 Azure 估算的 30 天费用和节省（约等于每月），按当前用量计算，未考虑降配；先降配并稳定后再按新的用量采购。同一订阅的 1 年和 3 年、预留实例和节省计划是互相替代的方案，节省不能相加。</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>资源类型</t>
+  </si>
+  <si>
+    <t>规格</t>
+  </si>
+  <si>
+    <t>建议数量或每小时承诺</t>
+  </si>
+  <si>
+    <t>30天按需费用USD</t>
+  </si>
+  <si>
+    <t>购买后费用USD</t>
+  </si>
+  <si>
+    <t>估算节省USD（30天）</t>
+  </si>
+  <si>
+    <t>VirtualMachines</t>
+  </si>
+  <si>
+    <t>japaneast</t>
+  </si>
+  <si>
+    <t>3 年</t>
+  </si>
+  <si>
+    <t>Compute_Savings_Plan</t>
+  </si>
+  <si>
+    <t>每小时承诺 0.95</t>
+  </si>
+  <si>
     <t>建议清单和执行跟踪</t>
   </si>
   <si>
     <t>预计节省不是已实现节省；当前检查建议与历史费用分别标注。</t>
   </si>
   <si>
-    <t>范围</t>
-  </si>
-  <si>
     <t>发现</t>
   </si>
   <si>
@@ -1257,7 +1392,7 @@
     <t>长期稳定计算、数据库、缓存及可预留存储费用</t>
   </si>
   <si>
-    <t>已有按服务列表价对比；是否有闲置承诺需结合现有订单及使用记录核对</t>
+    <t>9月分摊费用中 8.3% 由 RI/SP 覆盖；现有 2 个预留、1 个节省计划，其中 1 个近 30 天未用满，1 个即将到期；Azure 基于过去 30 天用量估算，购买 1 年期预留实例约节省 USD 128.62，购买 1 年期节省计划约节省 USD 188.60（每 30 天，按当前用量、未计入降配；预留实例和节省计划覆盖同一部分用量，只能选其一，3 年期方案见 Excel）</t>
   </si>
   <si>
     <t>先确定调整后的长期用量，再比较适用的1年/3年RI和SP；不要按全年满配估算直接采购</t>
@@ -1338,15 +1473,6 @@
     <t>按每日平均值计算9月加权平均。规格为10月26日的当前配置，不一定是9月配置。CPU和内存都低于20%只表示可做容量评审，不代表可以直接降配。</t>
   </si>
   <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>规格</t>
-  </si>
-  <si>
     <t>9月费用USD</t>
   </si>
   <si>
@@ -1380,9 +1506,6 @@
     <t>Standard_D4ds_v4</t>
   </si>
   <si>
-    <t>japaneast</t>
-  </si>
-  <si>
     <t>CPU和内存9月平均均低于20%，建议容量评审</t>
   </si>
   <si>
@@ -1627,6 +1750,24 @@
   </si>
   <si>
     <t>对5个有费用订阅查询预算：4个无预算记录，shop-prod有月度USD 15,000预算；其余1个订阅未查询预算。年度累计支出不作为9月超预算证明</t>
+  </si>
+  <si>
+    <t>RI/SP 覆盖（按资源）</t>
+  </si>
+  <si>
+    <t>4 个有费用的订阅读取成功（9月分摊费用，按资源和计价方式）</t>
+  </si>
+  <si>
+    <t>RI/SP 现有订单</t>
+  </si>
+  <si>
+    <t>预留：读取成功；节省计划：读取成功</t>
+  </si>
+  <si>
+    <t>Azure 购买建议</t>
+  </si>
+  <si>
+    <t>6/6 次查询成功，共 3 条建议</t>
   </si>
   <si>
     <t>按区域费用</t>
@@ -2158,7 +2299,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-74B2-42B4-9DA5-487FA8472E6D}"/>
+              <c16:uniqueId val="{00000000-B053-4822-A0CB-B1770A835C3E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2480,7 +2621,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-74B2-42B4-9DA5-487FA8472E6D}"/>
+              <c16:uniqueId val="{00000001-B053-4822-A0CB-B1770A835C3E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2778,7 +2919,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-110A-4306-A70F-3E27673AAEC3}"/>
+              <c16:uniqueId val="{00000000-753A-4C6B-8439-D87CB773F152}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2935,7 +3076,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-110A-4306-A70F-3E27673AAEC3}"/>
+              <c16:uniqueId val="{00000001-753A-4C6B-8439-D87CB773F152}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3170,7 +3311,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-110A-4306-A70F-3E27673AAEC3}"/>
+              <c16:uniqueId val="{00000002-753A-4C6B-8439-D87CB773F152}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3337,7 +3478,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D017-4DDE-96D5-91756C15346E}"/>
+              <c16:uniqueId val="{00000000-0F8D-48FF-908F-07C42B280513}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3425,7 +3566,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D017-4DDE-96D5-91756C15346E}"/>
+              <c16:uniqueId val="{00000001-0F8D-48FF-908F-07C42B280513}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3549,7 +3690,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-1F2F-4813-B831-5CAB723525E7}"/>
+                <c16:uniqueId val="{00000001-7042-4AB8-A216-A2A24AE1475A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3570,7 +3711,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-1F2F-4813-B831-5CAB723525E7}"/>
+                <c16:uniqueId val="{00000003-7042-4AB8-A216-A2A24AE1475A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3591,7 +3732,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-1F2F-4813-B831-5CAB723525E7}"/>
+                <c16:uniqueId val="{00000005-7042-4AB8-A216-A2A24AE1475A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3612,7 +3753,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-1F2F-4813-B831-5CAB723525E7}"/>
+                <c16:uniqueId val="{00000007-7042-4AB8-A216-A2A24AE1475A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3622,7 +3763,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-1F2F-4813-B831-5CAB723525E7}"/>
+                <c16:uniqueId val="{00000009-7042-4AB8-A216-A2A24AE1475A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3632,7 +3773,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-1F2F-4813-B831-5CAB723525E7}"/>
+                <c16:uniqueId val="{0000000B-7042-4AB8-A216-A2A24AE1475A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3642,7 +3783,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-1F2F-4813-B831-5CAB723525E7}"/>
+                <c16:uniqueId val="{0000000D-7042-4AB8-A216-A2A24AE1475A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3652,7 +3793,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-1F2F-4813-B831-5CAB723525E7}"/>
+                <c16:uniqueId val="{0000000F-7042-4AB8-A216-A2A24AE1475A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3662,7 +3803,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-1F2F-4813-B831-5CAB723525E7}"/>
+                <c16:uniqueId val="{00000011-7042-4AB8-A216-A2A24AE1475A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3672,7 +3813,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-1F2F-4813-B831-5CAB723525E7}"/>
+                <c16:uniqueId val="{00000013-7042-4AB8-A216-A2A24AE1475A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3755,7 +3896,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000014-1F2F-4813-B831-5CAB723525E7}"/>
+              <c16:uniqueId val="{00000014-7042-4AB8-A216-A2A24AE1475A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3875,7 +4016,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-7ADC-4746-B3D5-6F9AE7B46876}"/>
+                <c16:uniqueId val="{00000001-1F94-48D9-B4C9-8FE5828FB4FA}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3896,7 +4037,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-7ADC-4746-B3D5-6F9AE7B46876}"/>
+                <c16:uniqueId val="{00000003-1F94-48D9-B4C9-8FE5828FB4FA}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3931,7 +4072,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-7ADC-4746-B3D5-6F9AE7B46876}"/>
+              <c16:uniqueId val="{00000004-1F94-48D9-B4C9-8FE5828FB4FA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6247,7 +6388,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -6422,8 +6563,30 @@
         <v>17350.942500000001</v>
       </c>
     </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C17" s="12">
+        <v>2357.2800000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C18" s="5">
+        <v>214.28</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:C16" xr:uid="{00000000-0009-0000-0000-00000D000000}"/>
+  <autoFilter ref="A3:C18" xr:uid="{00000000-0009-0000-0000-00000D000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
@@ -6435,6 +6598,342 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="9" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+    </row>
+    <row r="2" spans="1:9" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+    </row>
+    <row r="3" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="F4" s="5">
+        <v>99</v>
+      </c>
+      <c r="G4" s="5">
+        <v>98.5</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F5" s="12">
+        <v>0</v>
+      </c>
+      <c r="G5" s="12">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="25" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="F6" s="5">
+        <v>99.6</v>
+      </c>
+      <c r="G6" s="5">
+        <v>99.2</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:I6" xr:uid="{00000000-0009-0000-0000-00000E000000}"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="10" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+    </row>
+    <row r="2" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
+        <v>380</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+    </row>
+    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>357.12</v>
+      </c>
+      <c r="I4" s="5">
+        <v>228.5</v>
+      </c>
+      <c r="J4" s="5">
+        <v>128.62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="G5" s="12">
+        <v>2</v>
+      </c>
+      <c r="H5" s="12">
+        <v>357.12</v>
+      </c>
+      <c r="I5" s="12">
+        <v>146.4</v>
+      </c>
+      <c r="J5" s="12">
+        <v>210.72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1062</v>
+      </c>
+      <c r="I6" s="5">
+        <v>873.4</v>
+      </c>
+      <c r="J6" s="5">
+        <v>188.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J6" xr:uid="{00000000-0009-0000-0000-00000F000000}"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6449,7 +6948,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>349</v>
+        <v>393</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -6465,7 +6964,7 @@
     </row>
     <row r="2" spans="1:12" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>350</v>
+        <v>394</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -6484,61 +6983,61 @@
         <v>344</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>352</v>
+        <v>395</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>353</v>
+        <v>396</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>354</v>
+        <v>397</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>355</v>
+        <v>398</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>357</v>
+        <v>400</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>358</v>
+        <v>401</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>359</v>
+        <v>402</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>360</v>
+        <v>403</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>361</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>362</v>
+        <v>405</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>363</v>
+        <v>406</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>364</v>
+        <v>407</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>365</v>
+        <v>408</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4" t="s">
-        <v>366</v>
+        <v>409</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>367</v>
+        <v>410</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>368</v>
+        <v>411</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
@@ -6547,26 +7046,26 @@
     </row>
     <row r="5" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>362</v>
+        <v>405</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>369</v>
+        <v>412</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>370</v>
+        <v>413</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>371</v>
+        <v>414</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>366</v>
+        <v>409</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>367</v>
+        <v>410</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>368</v>
+        <v>411</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -6575,26 +7074,26 @@
     </row>
     <row r="6" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>362</v>
+        <v>405</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>372</v>
+        <v>415</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>373</v>
+        <v>416</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>374</v>
+        <v>417</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
-        <v>366</v>
+        <v>409</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>367</v>
+        <v>410</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>368</v>
+        <v>411</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -6603,26 +7102,26 @@
     </row>
     <row r="7" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>362</v>
+        <v>405</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>375</v>
+        <v>418</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>376</v>
+        <v>419</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>366</v>
+        <v>409</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>367</v>
+        <v>410</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>368</v>
+        <v>411</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -6631,28 +7130,28 @@
     </row>
     <row r="8" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>378</v>
+        <v>421</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>379</v>
+        <v>422</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>380</v>
+        <v>423</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>381</v>
+        <v>424</v>
       </c>
       <c r="E8" s="5">
         <v>760.51400000000001</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>382</v>
+        <v>425</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>383</v>
+        <v>426</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>384</v>
+        <v>427</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
@@ -6661,26 +7160,26 @@
     </row>
     <row r="9" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>385</v>
+        <v>428</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>386</v>
+        <v>429</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>387</v>
+        <v>430</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>388</v>
+        <v>431</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>389</v>
+        <v>432</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>390</v>
+        <v>433</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>391</v>
+        <v>434</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -6689,26 +7188,26 @@
     </row>
     <row r="10" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>392</v>
+        <v>435</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>393</v>
+        <v>436</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>394</v>
+        <v>437</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>395</v>
+        <v>438</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4" t="s">
-        <v>396</v>
+        <v>439</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>397</v>
+        <v>440</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>398</v>
+        <v>441</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -6717,26 +7216,26 @@
     </row>
     <row r="11" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>399</v>
+        <v>442</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>400</v>
+        <v>443</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>401</v>
+        <v>444</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>402</v>
+        <v>445</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>403</v>
+        <v>446</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>367</v>
+        <v>410</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>404</v>
+        <v>447</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -6745,26 +7244,26 @@
     </row>
     <row r="12" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>405</v>
+        <v>448</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>406</v>
+        <v>449</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>407</v>
+        <v>450</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>408</v>
+        <v>451</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4" t="s">
-        <v>409</v>
+        <v>452</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>410</v>
+        <v>453</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>411</v>
+        <v>454</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -6772,7 +7271,7 @@
       <c r="L12" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L12" xr:uid="{00000000-0009-0000-0000-00000E000000}"/>
+  <autoFilter ref="A3:L12" xr:uid="{00000000-0009-0000-0000-000010000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
@@ -6782,8 +7281,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6794,7 +7293,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>412</v>
+        <v>455</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -6811,7 +7310,7 @@
     </row>
     <row r="2" spans="1:13" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>413</v>
+        <v>456</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -6834,34 +7333,34 @@
         <v>244</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>414</v>
+        <v>354</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>415</v>
+        <v>381</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>150</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>417</v>
+        <v>457</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>418</v>
+        <v>458</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>419</v>
+        <v>459</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>421</v>
+        <v>461</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>422</v>
+        <v>462</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>4</v>
@@ -6878,13 +7377,13 @@
         <v>260</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>423</v>
+        <v>463</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>424</v>
+        <v>464</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>425</v>
+        <v>465</v>
       </c>
       <c r="G4" s="5">
         <v>1245</v>
@@ -6915,13 +7414,13 @@
         <v>266</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>426</v>
+        <v>466</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>427</v>
+        <v>467</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="G5" s="12">
         <v>708</v>
@@ -6940,7 +7439,7 @@
         <v>30</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>429</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -6954,13 +7453,13 @@
         <v>264</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>426</v>
+        <v>466</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>427</v>
+        <v>467</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="G6" s="5">
         <v>708</v>
@@ -6991,13 +7490,13 @@
         <v>268</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>423</v>
+        <v>463</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>430</v>
+        <v>469</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="G7" s="12">
         <v>572.70000000000005</v>
@@ -7016,7 +7515,7 @@
         <v>23</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>431</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="25" x14ac:dyDescent="0.35">
@@ -7030,13 +7529,13 @@
         <v>274</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>432</v>
+        <v>471</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="G8" s="5">
         <v>396</v>
@@ -7055,7 +7554,7 @@
         <v>30</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>434</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -7069,13 +7568,13 @@
         <v>298</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>426</v>
+        <v>466</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>435</v>
+        <v>474</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="G9" s="12">
         <v>123</v>
@@ -7094,11 +7593,11 @@
         <v>30</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>429</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M9" xr:uid="{00000000-0009-0000-0000-00000F000000}"/>
+  <autoFilter ref="A3:M9" xr:uid="{00000000-0009-0000-0000-000011000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
@@ -7108,8 +7607,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -7121,7 +7620,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>436</v>
+        <v>475</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -7138,7 +7637,7 @@
     </row>
     <row r="2" spans="1:13" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>437</v>
+        <v>476</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -7161,37 +7660,37 @@
         <v>244</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>438</v>
+        <v>477</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>439</v>
+        <v>478</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>440</v>
+        <v>479</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>441</v>
+        <v>480</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>442</v>
+        <v>481</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>443</v>
+        <v>482</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>444</v>
+        <v>483</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>445</v>
+        <v>484</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>446</v>
+        <v>485</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>447</v>
+        <v>486</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>417</v>
+        <v>457</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -7205,10 +7704,10 @@
         <v>270</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>448</v>
+        <v>487</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>449</v>
+        <v>488</v>
       </c>
       <c r="F4" s="5">
         <v>22340</v>
@@ -7223,13 +7722,13 @@
         <v>18.170000000000002</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>450</v>
+        <v>489</v>
       </c>
       <c r="K4" s="5">
         <v>310</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>451</v>
+        <v>490</v>
       </c>
       <c r="M4" s="5">
         <v>477.65</v>
@@ -7246,10 +7745,10 @@
         <v>300</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>448</v>
+        <v>487</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>449</v>
+        <v>488</v>
       </c>
       <c r="F5" s="12">
         <v>4750</v>
@@ -7264,13 +7763,13 @@
         <v>10.95</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>452</v>
+        <v>491</v>
       </c>
       <c r="K5" s="12">
         <v>2400</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>453</v>
+        <v>492</v>
       </c>
       <c r="M5" s="12">
         <v>98.37</v>
@@ -7287,10 +7786,10 @@
         <v>326</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>448</v>
+        <v>487</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>449</v>
+        <v>488</v>
       </c>
       <c r="F6" s="5">
         <v>662</v>
@@ -7305,250 +7804,23 @@
         <v>8.76</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>454</v>
+        <v>493</v>
       </c>
       <c r="K6" s="5">
         <v>12</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>451</v>
+        <v>490</v>
       </c>
       <c r="M6" s="5">
         <v>13.54</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M6" xr:uid="{00000000-0009-0000-0000-000010000000}"/>
+  <autoFilter ref="A3:M6" xr:uid="{00000000-0009-0000-0000-000012000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="80" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
-        <v>455</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-    </row>
-    <row r="2" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
-        <v>456</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-    </row>
-    <row r="3" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="25" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="C4" s="5">
-        <v>3556.31</v>
-      </c>
-      <c r="D4" s="5">
-        <v>1290</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="F4" s="5">
-        <v>30</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="25" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C5" s="12">
-        <v>1815.53</v>
-      </c>
-      <c r="D5" s="12">
-        <v>560</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="F5" s="12">
-        <v>30</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>467</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:H5" xr:uid="{00000000-0009-0000-0000-000011000000}"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="9" width="24" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
-        <v>468</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-    </row>
-    <row r="2" spans="1:9" ht="52" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
-        <v>469</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-    </row>
-    <row r="3" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="C4" s="5">
-        <v>15000</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="H4" s="5">
-        <v>11840</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>482</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:I4" xr:uid="{00000000-0009-0000-0000-000012000000}"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
@@ -9190,7 +9462,234 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>494</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+    </row>
+    <row r="2" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
+        <v>495</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+    </row>
+    <row r="3" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="5">
+        <v>3556.31</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1290</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="F4" s="5">
+        <v>30</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5" s="12">
+        <v>1815.53</v>
+      </c>
+      <c r="D5" s="12">
+        <v>560</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="F5" s="12">
+        <v>30</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:H5" xr:uid="{00000000-0009-0000-0000-000013000000}"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="9" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+    </row>
+    <row r="2" spans="1:9" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
+        <v>508</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+    </row>
+    <row r="3" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C4" s="5">
+        <v>15000</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="H4" s="5">
+        <v>11840</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>521</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:I4" xr:uid="{00000000-0009-0000-0000-000014000000}"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -9199,13 +9698,13 @@
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>483</v>
+        <v>522</v>
       </c>
       <c r="B1" s="17"/>
     </row>
     <row r="2" spans="1:2" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>484</v>
+        <v>523</v>
       </c>
       <c r="B2" s="18"/>
     </row>
@@ -9219,26 +9718,26 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>485</v>
+        <v>524</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>487</v>
+        <v>526</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>488</v>
+        <v>527</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -9246,169 +9745,193 @@
         <v>250</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>489</v>
+        <v>528</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="25" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>491</v>
+        <v>530</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>493</v>
+        <v>532</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>495</v>
+        <v>534</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>498</v>
+        <v>537</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>500</v>
+        <v>539</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>502</v>
+        <v>541</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>504</v>
+        <v>543</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>506</v>
+        <v>545</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>507</v>
+        <v>546</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>508</v>
+        <v>547</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="25" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>509</v>
+        <v>548</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>510</v>
+        <v>549</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>511</v>
+        <v>550</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="25" x14ac:dyDescent="0.35">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>513</v>
+        <v>552</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>514</v>
+        <v>553</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>515</v>
+        <v>554</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="25" x14ac:dyDescent="0.35">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>517</v>
+        <v>556</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="25" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>438</v>
+        <v>558</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="25" x14ac:dyDescent="0.35">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>520</v>
+        <v>560</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="25" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>522</v>
+        <v>562</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>523</v>
+        <v>563</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>524</v>
+        <v>477</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>525</v>
+        <v>564</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="25" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>570</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B26" xr:uid="{00000000-0009-0000-0000-000013000000}"/>
+  <autoFilter ref="A3:B29" xr:uid="{00000000-0009-0000-0000-000015000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B17" r:id="rId1" xr:uid="{00000000-0004-0000-1300-000000000000}"/>
+    <hyperlink ref="B17" r:id="rId1" xr:uid="{00000000-0004-0000-1500-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-kk_29knp\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-lhcbnfs4\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32655BD-CD7D-411F-B663-FC2D44C9880D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50E3BD1-B771-45F7-BC59-1A52134C66E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3645" yWindow="-13320" windowWidth="5970" windowHeight="10455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17190" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月度总览" sheetId="1" r:id="rId1"/>
@@ -174,7 +174,7 @@
     <t>数据查询时间</t>
   </si>
   <si>
-    <t>2026-10-27T06:11:07.154271+00:00</t>
+    <t>2026-10-27T09:26:35.021356+00:00</t>
   </si>
   <si>
     <t>完整月份费用按查询时结果列示</t>
@@ -2299,7 +2299,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B053-4822-A0CB-B1770A835C3E}"/>
+              <c16:uniqueId val="{00000000-CDAE-460F-BCCE-74A8137F1167}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2621,7 +2621,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-B053-4822-A0CB-B1770A835C3E}"/>
+              <c16:uniqueId val="{00000001-CDAE-460F-BCCE-74A8137F1167}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2919,7 +2919,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-753A-4C6B-8439-D87CB773F152}"/>
+              <c16:uniqueId val="{00000000-5E10-4462-AC03-E5B9BBD2724D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3076,7 +3076,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-753A-4C6B-8439-D87CB773F152}"/>
+              <c16:uniqueId val="{00000001-5E10-4462-AC03-E5B9BBD2724D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3311,7 +3311,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-753A-4C6B-8439-D87CB773F152}"/>
+              <c16:uniqueId val="{00000002-5E10-4462-AC03-E5B9BBD2724D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3478,7 +3478,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0F8D-48FF-908F-07C42B280513}"/>
+              <c16:uniqueId val="{00000000-B06F-45F8-A1FD-43F7D72A1C92}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3566,7 +3566,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0F8D-48FF-908F-07C42B280513}"/>
+              <c16:uniqueId val="{00000001-B06F-45F8-A1FD-43F7D72A1C92}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3690,7 +3690,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-7042-4AB8-A216-A2A24AE1475A}"/>
+                <c16:uniqueId val="{00000001-DB4A-4C4C-991C-1B1B262B3EB3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3711,7 +3711,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-7042-4AB8-A216-A2A24AE1475A}"/>
+                <c16:uniqueId val="{00000003-DB4A-4C4C-991C-1B1B262B3EB3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3732,7 +3732,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-7042-4AB8-A216-A2A24AE1475A}"/>
+                <c16:uniqueId val="{00000005-DB4A-4C4C-991C-1B1B262B3EB3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3753,7 +3753,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-7042-4AB8-A216-A2A24AE1475A}"/>
+                <c16:uniqueId val="{00000007-DB4A-4C4C-991C-1B1B262B3EB3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3763,7 +3763,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-7042-4AB8-A216-A2A24AE1475A}"/>
+                <c16:uniqueId val="{00000009-DB4A-4C4C-991C-1B1B262B3EB3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3773,7 +3773,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-7042-4AB8-A216-A2A24AE1475A}"/>
+                <c16:uniqueId val="{0000000B-DB4A-4C4C-991C-1B1B262B3EB3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3783,7 +3783,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-7042-4AB8-A216-A2A24AE1475A}"/>
+                <c16:uniqueId val="{0000000D-DB4A-4C4C-991C-1B1B262B3EB3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3793,7 +3793,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-7042-4AB8-A216-A2A24AE1475A}"/>
+                <c16:uniqueId val="{0000000F-DB4A-4C4C-991C-1B1B262B3EB3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3803,7 +3803,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-7042-4AB8-A216-A2A24AE1475A}"/>
+                <c16:uniqueId val="{00000011-DB4A-4C4C-991C-1B1B262B3EB3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3813,7 +3813,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-7042-4AB8-A216-A2A24AE1475A}"/>
+                <c16:uniqueId val="{00000013-DB4A-4C4C-991C-1B1B262B3EB3}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3896,7 +3896,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000014-7042-4AB8-A216-A2A24AE1475A}"/>
+              <c16:uniqueId val="{00000014-DB4A-4C4C-991C-1B1B262B3EB3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4016,7 +4016,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-1F94-48D9-B4C9-8FE5828FB4FA}"/>
+                <c16:uniqueId val="{00000001-B1FA-42F5-84AC-FB2EB795E11C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4037,7 +4037,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-1F94-48D9-B4C9-8FE5828FB4FA}"/>
+                <c16:uniqueId val="{00000003-B1FA-42F5-84AC-FB2EB795E11C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4072,7 +4072,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-1F94-48D9-B4C9-8FE5828FB4FA}"/>
+              <c16:uniqueId val="{00000004-B1FA-42F5-84AC-FB2EB795E11C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-lhcbnfs4\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-yb_0tvu1\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50E3BD1-B771-45F7-BC59-1A52134C66E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7CB789-C94B-4F32-AEED-2718A9E86021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17190" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -174,7 +174,7 @@
     <t>数据查询时间</t>
   </si>
   <si>
-    <t>2026-10-27T09:26:35.021356+00:00</t>
+    <t>2026-10-27T09:56:53.145316+00:00</t>
   </si>
   <si>
     <t>完整月份费用按查询时结果列示</t>
@@ -2299,7 +2299,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CDAE-460F-BCCE-74A8137F1167}"/>
+              <c16:uniqueId val="{00000000-2C6F-4FAE-9EB0-C59B49A42ADE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2621,7 +2621,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-CDAE-460F-BCCE-74A8137F1167}"/>
+              <c16:uniqueId val="{00000001-2C6F-4FAE-9EB0-C59B49A42ADE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2919,7 +2919,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5E10-4462-AC03-E5B9BBD2724D}"/>
+              <c16:uniqueId val="{00000000-C503-49C3-9E91-6C224CBF0505}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3076,7 +3076,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5E10-4462-AC03-E5B9BBD2724D}"/>
+              <c16:uniqueId val="{00000001-C503-49C3-9E91-6C224CBF0505}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3311,7 +3311,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-5E10-4462-AC03-E5B9BBD2724D}"/>
+              <c16:uniqueId val="{00000002-C503-49C3-9E91-6C224CBF0505}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3478,7 +3478,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B06F-45F8-A1FD-43F7D72A1C92}"/>
+              <c16:uniqueId val="{00000000-DA88-423D-BC40-4BE8BF19FCB0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3566,7 +3566,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-B06F-45F8-A1FD-43F7D72A1C92}"/>
+              <c16:uniqueId val="{00000001-DA88-423D-BC40-4BE8BF19FCB0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3690,7 +3690,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-DB4A-4C4C-991C-1B1B262B3EB3}"/>
+                <c16:uniqueId val="{00000001-2E03-4E45-8C3C-EF6D9017B789}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3711,7 +3711,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-DB4A-4C4C-991C-1B1B262B3EB3}"/>
+                <c16:uniqueId val="{00000003-2E03-4E45-8C3C-EF6D9017B789}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3732,7 +3732,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-DB4A-4C4C-991C-1B1B262B3EB3}"/>
+                <c16:uniqueId val="{00000005-2E03-4E45-8C3C-EF6D9017B789}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3753,7 +3753,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-DB4A-4C4C-991C-1B1B262B3EB3}"/>
+                <c16:uniqueId val="{00000007-2E03-4E45-8C3C-EF6D9017B789}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3763,7 +3763,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-DB4A-4C4C-991C-1B1B262B3EB3}"/>
+                <c16:uniqueId val="{00000009-2E03-4E45-8C3C-EF6D9017B789}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3773,7 +3773,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-DB4A-4C4C-991C-1B1B262B3EB3}"/>
+                <c16:uniqueId val="{0000000B-2E03-4E45-8C3C-EF6D9017B789}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3783,7 +3783,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-DB4A-4C4C-991C-1B1B262B3EB3}"/>
+                <c16:uniqueId val="{0000000D-2E03-4E45-8C3C-EF6D9017B789}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3793,7 +3793,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-DB4A-4C4C-991C-1B1B262B3EB3}"/>
+                <c16:uniqueId val="{0000000F-2E03-4E45-8C3C-EF6D9017B789}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3803,7 +3803,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-DB4A-4C4C-991C-1B1B262B3EB3}"/>
+                <c16:uniqueId val="{00000011-2E03-4E45-8C3C-EF6D9017B789}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3813,7 +3813,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-DB4A-4C4C-991C-1B1B262B3EB3}"/>
+                <c16:uniqueId val="{00000013-2E03-4E45-8C3C-EF6D9017B789}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3896,7 +3896,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000014-DB4A-4C4C-991C-1B1B262B3EB3}"/>
+              <c16:uniqueId val="{00000014-2E03-4E45-8C3C-EF6D9017B789}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4016,7 +4016,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-B1FA-42F5-84AC-FB2EB795E11C}"/>
+                <c16:uniqueId val="{00000001-9C40-4E57-8554-7ADD845FB129}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4037,7 +4037,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-B1FA-42F5-84AC-FB2EB795E11C}"/>
+                <c16:uniqueId val="{00000003-9C40-4E57-8554-7ADD845FB129}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4072,7 +4072,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-B1FA-42F5-84AC-FB2EB795E11C}"/>
+              <c16:uniqueId val="{00000004-9C40-4E57-8554-7ADD845FB129}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-yb_0tvu1\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-09jfy2fk\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7CB789-C94B-4F32-AEED-2718A9E86021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D5C424-AF14-4533-B02D-5D7F4B5843EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17190" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月度总览" sheetId="1" r:id="rId1"/>
@@ -174,7 +174,7 @@
     <t>数据查询时间</t>
   </si>
   <si>
-    <t>2026-10-27T09:56:53.145316+00:00</t>
+    <t>2026-10-27T11:07:34.418527+00:00</t>
   </si>
   <si>
     <t>完整月份费用按查询时结果列示</t>
@@ -2299,7 +2299,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2C6F-4FAE-9EB0-C59B49A42ADE}"/>
+              <c16:uniqueId val="{00000000-3457-4E81-9BFD-345C9B0DA903}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2621,7 +2621,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-2C6F-4FAE-9EB0-C59B49A42ADE}"/>
+              <c16:uniqueId val="{00000001-3457-4E81-9BFD-345C9B0DA903}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2919,7 +2919,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C503-49C3-9E91-6C224CBF0505}"/>
+              <c16:uniqueId val="{00000000-003B-46F4-B6C4-C4C2F0C11223}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3076,7 +3076,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C503-49C3-9E91-6C224CBF0505}"/>
+              <c16:uniqueId val="{00000001-003B-46F4-B6C4-C4C2F0C11223}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3311,7 +3311,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C503-49C3-9E91-6C224CBF0505}"/>
+              <c16:uniqueId val="{00000002-003B-46F4-B6C4-C4C2F0C11223}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3478,7 +3478,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DA88-423D-BC40-4BE8BF19FCB0}"/>
+              <c16:uniqueId val="{00000000-892B-4954-9FEE-18BF2F404375}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3566,7 +3566,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-DA88-423D-BC40-4BE8BF19FCB0}"/>
+              <c16:uniqueId val="{00000001-892B-4954-9FEE-18BF2F404375}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3690,7 +3690,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-2E03-4E45-8C3C-EF6D9017B789}"/>
+                <c16:uniqueId val="{00000001-B39C-4ABA-B8D9-E8F74823366A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3711,7 +3711,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-2E03-4E45-8C3C-EF6D9017B789}"/>
+                <c16:uniqueId val="{00000003-B39C-4ABA-B8D9-E8F74823366A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3732,7 +3732,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-2E03-4E45-8C3C-EF6D9017B789}"/>
+                <c16:uniqueId val="{00000005-B39C-4ABA-B8D9-E8F74823366A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3753,7 +3753,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-2E03-4E45-8C3C-EF6D9017B789}"/>
+                <c16:uniqueId val="{00000007-B39C-4ABA-B8D9-E8F74823366A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3763,7 +3763,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-2E03-4E45-8C3C-EF6D9017B789}"/>
+                <c16:uniqueId val="{00000009-B39C-4ABA-B8D9-E8F74823366A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3773,7 +3773,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-2E03-4E45-8C3C-EF6D9017B789}"/>
+                <c16:uniqueId val="{0000000B-B39C-4ABA-B8D9-E8F74823366A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3783,7 +3783,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-2E03-4E45-8C3C-EF6D9017B789}"/>
+                <c16:uniqueId val="{0000000D-B39C-4ABA-B8D9-E8F74823366A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3793,7 +3793,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-2E03-4E45-8C3C-EF6D9017B789}"/>
+                <c16:uniqueId val="{0000000F-B39C-4ABA-B8D9-E8F74823366A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3803,7 +3803,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-2E03-4E45-8C3C-EF6D9017B789}"/>
+                <c16:uniqueId val="{00000011-B39C-4ABA-B8D9-E8F74823366A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3813,7 +3813,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-2E03-4E45-8C3C-EF6D9017B789}"/>
+                <c16:uniqueId val="{00000013-B39C-4ABA-B8D9-E8F74823366A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3896,7 +3896,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000014-2E03-4E45-8C3C-EF6D9017B789}"/>
+              <c16:uniqueId val="{00000014-B39C-4ABA-B8D9-E8F74823366A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4016,7 +4016,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-9C40-4E57-8554-7ADD845FB129}"/>
+                <c16:uniqueId val="{00000001-222E-4B43-95DD-FA6384CE96EC}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4037,7 +4037,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-9C40-4E57-8554-7ADD845FB129}"/>
+                <c16:uniqueId val="{00000003-222E-4B43-95DD-FA6384CE96EC}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4072,7 +4072,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-9C40-4E57-8554-7ADD845FB129}"/>
+              <c16:uniqueId val="{00000004-222E-4B43-95DD-FA6384CE96EC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-09jfy2fk\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-5yxkm8zf\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D5C424-AF14-4533-B02D-5D7F4B5843EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F49538-5D05-4D5D-80E1-0230AB7F2425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月度总览" sheetId="1" r:id="rId1"/>
@@ -174,7 +174,7 @@
     <t>数据查询时间</t>
   </si>
   <si>
-    <t>2026-10-27T11:07:34.418527+00:00</t>
+    <t>2026-10-27T13:22:17.643676+00:00</t>
   </si>
   <si>
     <t>完整月份费用按查询时结果列示</t>
@@ -2299,7 +2299,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3457-4E81-9BFD-345C9B0DA903}"/>
+              <c16:uniqueId val="{00000000-007C-47FC-A99D-0FBF4454EF5B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2621,7 +2621,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3457-4E81-9BFD-345C9B0DA903}"/>
+              <c16:uniqueId val="{00000001-007C-47FC-A99D-0FBF4454EF5B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2919,7 +2919,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-003B-46F4-B6C4-C4C2F0C11223}"/>
+              <c16:uniqueId val="{00000000-970D-4754-9EEC-3988779DEB96}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3076,7 +3076,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-003B-46F4-B6C4-C4C2F0C11223}"/>
+              <c16:uniqueId val="{00000001-970D-4754-9EEC-3988779DEB96}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3311,7 +3311,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-003B-46F4-B6C4-C4C2F0C11223}"/>
+              <c16:uniqueId val="{00000002-970D-4754-9EEC-3988779DEB96}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3478,7 +3478,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-892B-4954-9FEE-18BF2F404375}"/>
+              <c16:uniqueId val="{00000000-6CBD-42CD-8227-C439FCE341B0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3566,7 +3566,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-892B-4954-9FEE-18BF2F404375}"/>
+              <c16:uniqueId val="{00000001-6CBD-42CD-8227-C439FCE341B0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3690,7 +3690,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-B39C-4ABA-B8D9-E8F74823366A}"/>
+                <c16:uniqueId val="{00000001-D52D-408B-A451-968906E92EF7}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3711,7 +3711,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-B39C-4ABA-B8D9-E8F74823366A}"/>
+                <c16:uniqueId val="{00000003-D52D-408B-A451-968906E92EF7}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3732,7 +3732,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-B39C-4ABA-B8D9-E8F74823366A}"/>
+                <c16:uniqueId val="{00000005-D52D-408B-A451-968906E92EF7}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3753,7 +3753,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-B39C-4ABA-B8D9-E8F74823366A}"/>
+                <c16:uniqueId val="{00000007-D52D-408B-A451-968906E92EF7}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3763,7 +3763,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-B39C-4ABA-B8D9-E8F74823366A}"/>
+                <c16:uniqueId val="{00000009-D52D-408B-A451-968906E92EF7}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3773,7 +3773,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-B39C-4ABA-B8D9-E8F74823366A}"/>
+                <c16:uniqueId val="{0000000B-D52D-408B-A451-968906E92EF7}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3783,7 +3783,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-B39C-4ABA-B8D9-E8F74823366A}"/>
+                <c16:uniqueId val="{0000000D-D52D-408B-A451-968906E92EF7}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3793,7 +3793,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-B39C-4ABA-B8D9-E8F74823366A}"/>
+                <c16:uniqueId val="{0000000F-D52D-408B-A451-968906E92EF7}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3803,7 +3803,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-B39C-4ABA-B8D9-E8F74823366A}"/>
+                <c16:uniqueId val="{00000011-D52D-408B-A451-968906E92EF7}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3813,7 +3813,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-B39C-4ABA-B8D9-E8F74823366A}"/>
+                <c16:uniqueId val="{00000013-D52D-408B-A451-968906E92EF7}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3896,7 +3896,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000014-B39C-4ABA-B8D9-E8F74823366A}"/>
+              <c16:uniqueId val="{00000014-D52D-408B-A451-968906E92EF7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4016,7 +4016,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-222E-4B43-95DD-FA6384CE96EC}"/>
+                <c16:uniqueId val="{00000001-632A-4C8C-B4DE-9E27BF84CC73}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4037,7 +4037,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-222E-4B43-95DD-FA6384CE96EC}"/>
+                <c16:uniqueId val="{00000003-632A-4C8C-B4DE-9E27BF84CC73}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4072,7 +4072,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-222E-4B43-95DD-FA6384CE96EC}"/>
+              <c16:uniqueId val="{00000004-632A-4C8C-B4DE-9E27BF84CC73}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-5yxkm8zf\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-do642wo4\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F49538-5D05-4D5D-80E1-0230AB7F2425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A6BD82-BC9E-4B96-8F67-21FDB21EFB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月度总览" sheetId="1" r:id="rId1"/>
@@ -174,7 +174,7 @@
     <t>数据查询时间</t>
   </si>
   <si>
-    <t>2026-10-27T13:22:17.643676+00:00</t>
+    <t>2026-10-29T15:39:31.447916+00:00</t>
   </si>
   <si>
     <t>完整月份费用按查询时结果列示</t>
@@ -1104,7 +1104,7 @@
     <t>10月费用预测（Azure Cost Management）</t>
   </si>
   <si>
-    <t>查询日期2026-10-27；已发生的日期为实际费用，其余为Azure预测值，不是账单金额。9月无费用的订阅预测接口不返回结果。</t>
+    <t>查询日期2026-10-29；已发生的日期为实际费用，其余为Azure预测值，不是账单金额。9月无费用的订阅预测接口不返回结果。</t>
   </si>
   <si>
     <t>10月截至查询日实际USD</t>
@@ -1236,7 +1236,7 @@
     <t>2026-12-15</t>
   </si>
   <si>
-    <t>49 天后到期，未设置自动续订</t>
+    <t>47 天后到期，未设置自动续订</t>
   </si>
   <si>
     <t>Azure 基于过去 30 天用量的 RI/SP 购买建议</t>
@@ -1779,7 +1779,7 @@
     <t>10月费用预测</t>
   </si>
   <si>
-    <t>查询日期2026-10-27；5个订阅有预测结果，其余0个订阅接口未返回预测；预测为Azure模型结果，不是账单</t>
+    <t>查询日期2026-10-29；5个订阅有预测结果，其余0个订阅接口未返回预测；预测为Azure模型结果，不是账单</t>
   </si>
   <si>
     <t>费用变化原因</t>
@@ -2299,7 +2299,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-007C-47FC-A99D-0FBF4454EF5B}"/>
+              <c16:uniqueId val="{00000000-D891-423F-A35E-E6FE9B69DC40}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2621,7 +2621,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-007C-47FC-A99D-0FBF4454EF5B}"/>
+              <c16:uniqueId val="{00000001-D891-423F-A35E-E6FE9B69DC40}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2919,7 +2919,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-970D-4754-9EEC-3988779DEB96}"/>
+              <c16:uniqueId val="{00000000-F4EB-468D-8E1C-C2C6F1B9B181}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3076,7 +3076,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-970D-4754-9EEC-3988779DEB96}"/>
+              <c16:uniqueId val="{00000001-F4EB-468D-8E1C-C2C6F1B9B181}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3311,7 +3311,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-970D-4754-9EEC-3988779DEB96}"/>
+              <c16:uniqueId val="{00000002-F4EB-468D-8E1C-C2C6F1B9B181}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3478,7 +3478,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6CBD-42CD-8227-C439FCE341B0}"/>
+              <c16:uniqueId val="{00000000-7F46-4394-AEAE-A4404A4E14EE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3566,7 +3566,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-6CBD-42CD-8227-C439FCE341B0}"/>
+              <c16:uniqueId val="{00000001-7F46-4394-AEAE-A4404A4E14EE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3690,7 +3690,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-D52D-408B-A451-968906E92EF7}"/>
+                <c16:uniqueId val="{00000001-6284-4195-B9CD-523042B86863}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3711,7 +3711,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-D52D-408B-A451-968906E92EF7}"/>
+                <c16:uniqueId val="{00000003-6284-4195-B9CD-523042B86863}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3732,7 +3732,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-D52D-408B-A451-968906E92EF7}"/>
+                <c16:uniqueId val="{00000005-6284-4195-B9CD-523042B86863}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3753,7 +3753,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-D52D-408B-A451-968906E92EF7}"/>
+                <c16:uniqueId val="{00000007-6284-4195-B9CD-523042B86863}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3763,7 +3763,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-D52D-408B-A451-968906E92EF7}"/>
+                <c16:uniqueId val="{00000009-6284-4195-B9CD-523042B86863}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3773,7 +3773,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-D52D-408B-A451-968906E92EF7}"/>
+                <c16:uniqueId val="{0000000B-6284-4195-B9CD-523042B86863}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3783,7 +3783,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-D52D-408B-A451-968906E92EF7}"/>
+                <c16:uniqueId val="{0000000D-6284-4195-B9CD-523042B86863}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3793,7 +3793,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-D52D-408B-A451-968906E92EF7}"/>
+                <c16:uniqueId val="{0000000F-6284-4195-B9CD-523042B86863}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3803,7 +3803,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-D52D-408B-A451-968906E92EF7}"/>
+                <c16:uniqueId val="{00000011-6284-4195-B9CD-523042B86863}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3813,7 +3813,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-D52D-408B-A451-968906E92EF7}"/>
+                <c16:uniqueId val="{00000013-6284-4195-B9CD-523042B86863}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3896,7 +3896,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000014-D52D-408B-A451-968906E92EF7}"/>
+              <c16:uniqueId val="{00000014-6284-4195-B9CD-523042B86863}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4016,7 +4016,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-632A-4C8C-B4DE-9E27BF84CC73}"/>
+                <c16:uniqueId val="{00000001-784C-49AB-A49E-0B52A1DDA608}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4037,7 +4037,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-632A-4C8C-B4DE-9E27BF84CC73}"/>
+                <c16:uniqueId val="{00000003-784C-49AB-A49E-0B52A1DDA608}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4072,7 +4072,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-632A-4C8C-B4DE-9E27BF84CC73}"/>
+              <c16:uniqueId val="{00000004-784C-49AB-A49E-0B52A1DDA608}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-do642wo4\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-jluf97rf\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A6BD82-BC9E-4B96-8F67-21FDB21EFB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6E0BEF-AD1A-4C38-B2BF-3F1D02FFA4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -174,7 +174,7 @@
     <t>数据查询时间</t>
   </si>
   <si>
-    <t>2026-10-29T15:39:31.447916+00:00</t>
+    <t>2026-10-29T15:57:22.064976+00:00</t>
   </si>
   <si>
     <t>完整月份费用按查询时结果列示</t>
@@ -2299,7 +2299,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D891-423F-A35E-E6FE9B69DC40}"/>
+              <c16:uniqueId val="{00000000-0A23-4011-91DA-497407C3DA81}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2621,7 +2621,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D891-423F-A35E-E6FE9B69DC40}"/>
+              <c16:uniqueId val="{00000001-0A23-4011-91DA-497407C3DA81}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2919,7 +2919,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F4EB-468D-8E1C-C2C6F1B9B181}"/>
+              <c16:uniqueId val="{00000000-3D27-479A-A455-1AA18D13F601}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3076,7 +3076,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-F4EB-468D-8E1C-C2C6F1B9B181}"/>
+              <c16:uniqueId val="{00000001-3D27-479A-A455-1AA18D13F601}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3311,7 +3311,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-F4EB-468D-8E1C-C2C6F1B9B181}"/>
+              <c16:uniqueId val="{00000002-3D27-479A-A455-1AA18D13F601}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3478,7 +3478,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7F46-4394-AEAE-A4404A4E14EE}"/>
+              <c16:uniqueId val="{00000000-5FCF-4854-87D4-57C5DB961339}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3566,7 +3566,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7F46-4394-AEAE-A4404A4E14EE}"/>
+              <c16:uniqueId val="{00000001-5FCF-4854-87D4-57C5DB961339}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3690,7 +3690,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-6284-4195-B9CD-523042B86863}"/>
+                <c16:uniqueId val="{00000001-665F-4B03-8975-492641CA1337}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3711,7 +3711,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-6284-4195-B9CD-523042B86863}"/>
+                <c16:uniqueId val="{00000003-665F-4B03-8975-492641CA1337}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3732,7 +3732,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-6284-4195-B9CD-523042B86863}"/>
+                <c16:uniqueId val="{00000005-665F-4B03-8975-492641CA1337}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3753,7 +3753,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-6284-4195-B9CD-523042B86863}"/>
+                <c16:uniqueId val="{00000007-665F-4B03-8975-492641CA1337}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3763,7 +3763,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-6284-4195-B9CD-523042B86863}"/>
+                <c16:uniqueId val="{00000009-665F-4B03-8975-492641CA1337}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3773,7 +3773,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-6284-4195-B9CD-523042B86863}"/>
+                <c16:uniqueId val="{0000000B-665F-4B03-8975-492641CA1337}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3783,7 +3783,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-6284-4195-B9CD-523042B86863}"/>
+                <c16:uniqueId val="{0000000D-665F-4B03-8975-492641CA1337}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3793,7 +3793,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-6284-4195-B9CD-523042B86863}"/>
+                <c16:uniqueId val="{0000000F-665F-4B03-8975-492641CA1337}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3803,7 +3803,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-6284-4195-B9CD-523042B86863}"/>
+                <c16:uniqueId val="{00000011-665F-4B03-8975-492641CA1337}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3813,7 +3813,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-6284-4195-B9CD-523042B86863}"/>
+                <c16:uniqueId val="{00000013-665F-4B03-8975-492641CA1337}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3896,7 +3896,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000014-6284-4195-B9CD-523042B86863}"/>
+              <c16:uniqueId val="{00000014-665F-4B03-8975-492641CA1337}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4016,7 +4016,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-784C-49AB-A49E-0B52A1DDA608}"/>
+                <c16:uniqueId val="{00000001-F9FD-4F72-9D77-6DB0200C338B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4037,7 +4037,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-784C-49AB-A49E-0B52A1DDA608}"/>
+                <c16:uniqueId val="{00000003-F9FD-4F72-9D77-6DB0200C338B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4072,7 +4072,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-784C-49AB-A49E-0B52A1DDA608}"/>
+              <c16:uniqueId val="{00000004-F9FD-4F72-9D77-6DB0200C338B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-jluf97rf\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-4z_oecii\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6E0BEF-AD1A-4C38-B2BF-3F1D02FFA4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACCEFFF-48CD-48B5-AAEB-85A0279E6AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月度总览" sheetId="1" r:id="rId1"/>
@@ -174,7 +174,7 @@
     <t>数据查询时间</t>
   </si>
   <si>
-    <t>2026-10-29T15:57:22.064976+00:00</t>
+    <t>2026-10-29T17:02:46.999275+00:00</t>
   </si>
   <si>
     <t>完整月份费用按查询时结果列示</t>
@@ -1104,7 +1104,7 @@
     <t>10月费用预测（Azure Cost Management）</t>
   </si>
   <si>
-    <t>查询日期2026-10-29；已发生的日期为实际费用，其余为Azure预测值，不是账单金额。9月无费用的订阅预测接口不返回结果。</t>
+    <t>查询日期2026-10-30；已发生的日期为实际费用，其余为Azure预测值，不是账单金额。9月无费用的订阅预测接口不返回结果。</t>
   </si>
   <si>
     <t>10月截至查询日实际USD</t>
@@ -1779,7 +1779,7 @@
     <t>10月费用预测</t>
   </si>
   <si>
-    <t>查询日期2026-10-29；5个订阅有预测结果，其余0个订阅接口未返回预测；预测为Azure模型结果，不是账单</t>
+    <t>查询日期2026-10-30；5个订阅有预测结果，其余0个订阅接口未返回预测；预测为Azure模型结果，不是账单</t>
   </si>
   <si>
     <t>费用变化原因</t>
@@ -2299,7 +2299,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0A23-4011-91DA-497407C3DA81}"/>
+              <c16:uniqueId val="{00000000-D45B-4E7D-9811-F01274454B7A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2621,7 +2621,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0A23-4011-91DA-497407C3DA81}"/>
+              <c16:uniqueId val="{00000001-D45B-4E7D-9811-F01274454B7A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2919,7 +2919,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3D27-479A-A455-1AA18D13F601}"/>
+              <c16:uniqueId val="{00000000-4F06-42EC-BE12-E9093014F3B5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3076,7 +3076,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3D27-479A-A455-1AA18D13F601}"/>
+              <c16:uniqueId val="{00000001-4F06-42EC-BE12-E9093014F3B5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3311,7 +3311,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3D27-479A-A455-1AA18D13F601}"/>
+              <c16:uniqueId val="{00000002-4F06-42EC-BE12-E9093014F3B5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3478,7 +3478,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5FCF-4854-87D4-57C5DB961339}"/>
+              <c16:uniqueId val="{00000000-C2D2-4485-BE61-6B50674C4D95}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3566,7 +3566,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5FCF-4854-87D4-57C5DB961339}"/>
+              <c16:uniqueId val="{00000001-C2D2-4485-BE61-6B50674C4D95}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3690,7 +3690,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-665F-4B03-8975-492641CA1337}"/>
+                <c16:uniqueId val="{00000001-6F70-4313-B4FA-491B36A13618}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3711,7 +3711,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-665F-4B03-8975-492641CA1337}"/>
+                <c16:uniqueId val="{00000003-6F70-4313-B4FA-491B36A13618}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3732,7 +3732,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-665F-4B03-8975-492641CA1337}"/>
+                <c16:uniqueId val="{00000005-6F70-4313-B4FA-491B36A13618}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3753,7 +3753,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-665F-4B03-8975-492641CA1337}"/>
+                <c16:uniqueId val="{00000007-6F70-4313-B4FA-491B36A13618}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3763,7 +3763,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-665F-4B03-8975-492641CA1337}"/>
+                <c16:uniqueId val="{00000009-6F70-4313-B4FA-491B36A13618}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3773,7 +3773,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-665F-4B03-8975-492641CA1337}"/>
+                <c16:uniqueId val="{0000000B-6F70-4313-B4FA-491B36A13618}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3783,7 +3783,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-665F-4B03-8975-492641CA1337}"/>
+                <c16:uniqueId val="{0000000D-6F70-4313-B4FA-491B36A13618}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3793,7 +3793,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-665F-4B03-8975-492641CA1337}"/>
+                <c16:uniqueId val="{0000000F-6F70-4313-B4FA-491B36A13618}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3803,7 +3803,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-665F-4B03-8975-492641CA1337}"/>
+                <c16:uniqueId val="{00000011-6F70-4313-B4FA-491B36A13618}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3813,7 +3813,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-665F-4B03-8975-492641CA1337}"/>
+                <c16:uniqueId val="{00000013-6F70-4313-B4FA-491B36A13618}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3896,7 +3896,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000014-665F-4B03-8975-492641CA1337}"/>
+              <c16:uniqueId val="{00000014-6F70-4313-B4FA-491B36A13618}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4016,7 +4016,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-F9FD-4F72-9D77-6DB0200C338B}"/>
+                <c16:uniqueId val="{00000001-9B7D-4670-A00A-6E0ECC9F71B0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4037,7 +4037,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-F9FD-4F72-9D77-6DB0200C338B}"/>
+                <c16:uniqueId val="{00000003-9B7D-4670-A00A-6E0ECC9F71B0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4072,7 +4072,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-F9FD-4F72-9D77-6DB0200C338B}"/>
+              <c16:uniqueId val="{00000004-9B7D-4670-A00A-6E0ECC9F71B0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-4z_oecii\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-gq0eyj71\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACCEFFF-48CD-48B5-AAEB-85A0279E6AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE099B5-AB77-448F-BF72-492477F01F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -174,7 +174,7 @@
     <t>数据查询时间</t>
   </si>
   <si>
-    <t>2026-10-29T17:02:46.999275+00:00</t>
+    <t>2026-10-29T18:20:54.376824+00:00</t>
   </si>
   <si>
     <t>完整月份费用按查询时结果列示</t>
@@ -2299,7 +2299,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D45B-4E7D-9811-F01274454B7A}"/>
+              <c16:uniqueId val="{00000000-CD0A-4D88-B8C3-17FAE29FD5C7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2621,7 +2621,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D45B-4E7D-9811-F01274454B7A}"/>
+              <c16:uniqueId val="{00000001-CD0A-4D88-B8C3-17FAE29FD5C7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2919,7 +2919,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4F06-42EC-BE12-E9093014F3B5}"/>
+              <c16:uniqueId val="{00000000-DD54-4197-BEE6-FDD0C113B966}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3076,7 +3076,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4F06-42EC-BE12-E9093014F3B5}"/>
+              <c16:uniqueId val="{00000001-DD54-4197-BEE6-FDD0C113B966}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3311,7 +3311,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-4F06-42EC-BE12-E9093014F3B5}"/>
+              <c16:uniqueId val="{00000002-DD54-4197-BEE6-FDD0C113B966}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3478,7 +3478,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C2D2-4485-BE61-6B50674C4D95}"/>
+              <c16:uniqueId val="{00000000-845C-4C60-AE8F-EFFEB870872C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3566,7 +3566,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C2D2-4485-BE61-6B50674C4D95}"/>
+              <c16:uniqueId val="{00000001-845C-4C60-AE8F-EFFEB870872C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3690,7 +3690,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-6F70-4313-B4FA-491B36A13618}"/>
+                <c16:uniqueId val="{00000001-C6D3-4861-81ED-0470CB27AB8A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3711,7 +3711,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-6F70-4313-B4FA-491B36A13618}"/>
+                <c16:uniqueId val="{00000003-C6D3-4861-81ED-0470CB27AB8A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3732,7 +3732,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-6F70-4313-B4FA-491B36A13618}"/>
+                <c16:uniqueId val="{00000005-C6D3-4861-81ED-0470CB27AB8A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3753,7 +3753,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-6F70-4313-B4FA-491B36A13618}"/>
+                <c16:uniqueId val="{00000007-C6D3-4861-81ED-0470CB27AB8A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3763,7 +3763,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-6F70-4313-B4FA-491B36A13618}"/>
+                <c16:uniqueId val="{00000009-C6D3-4861-81ED-0470CB27AB8A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3773,7 +3773,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-6F70-4313-B4FA-491B36A13618}"/>
+                <c16:uniqueId val="{0000000B-C6D3-4861-81ED-0470CB27AB8A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3783,7 +3783,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-6F70-4313-B4FA-491B36A13618}"/>
+                <c16:uniqueId val="{0000000D-C6D3-4861-81ED-0470CB27AB8A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3793,7 +3793,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-6F70-4313-B4FA-491B36A13618}"/>
+                <c16:uniqueId val="{0000000F-C6D3-4861-81ED-0470CB27AB8A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3803,7 +3803,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-6F70-4313-B4FA-491B36A13618}"/>
+                <c16:uniqueId val="{00000011-C6D3-4861-81ED-0470CB27AB8A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3813,7 +3813,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-6F70-4313-B4FA-491B36A13618}"/>
+                <c16:uniqueId val="{00000013-C6D3-4861-81ED-0470CB27AB8A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3896,7 +3896,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000014-6F70-4313-B4FA-491B36A13618}"/>
+              <c16:uniqueId val="{00000014-C6D3-4861-81ED-0470CB27AB8A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4016,7 +4016,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-9B7D-4670-A00A-6E0ECC9F71B0}"/>
+                <c16:uniqueId val="{00000001-2D80-4B5F-B85A-67EFFC6519DF}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4037,7 +4037,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-9B7D-4670-A00A-6E0ECC9F71B0}"/>
+                <c16:uniqueId val="{00000003-2D80-4B5F-B85A-67EFFC6519DF}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4072,7 +4072,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-9B7D-4670-A00A-6E0ECC9F71B0}"/>
+              <c16:uniqueId val="{00000004-2D80-4B5F-B85A-67EFFC6519DF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-gq0eyj71\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-9n18lti6\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE099B5-AB77-448F-BF72-492477F01F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE65942-75F1-42C1-96EA-153F6F2AFF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -174,7 +174,7 @@
     <t>数据查询时间</t>
   </si>
   <si>
-    <t>2026-10-29T18:20:54.376824+00:00</t>
+    <t>2026-10-29T21:12:04.445154+00:00</t>
   </si>
   <si>
     <t>完整月份费用按查询时结果列示</t>
@@ -894,18 +894,18 @@
     <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a4/resourcegroups/data-rg/providers/microsoft.cognitiveservices/accounts/data-openai</t>
   </si>
   <si>
+    <t>pay-mysql-prod</t>
+  </si>
+  <si>
+    <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a3/resourcegroups/pay-rg/providers/microsoft.dbformysql/flexibleservers/pay-mysql-prod</t>
+  </si>
+  <si>
     <t>shop-mysql-prod</t>
   </si>
   <si>
     <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a1/resourcegroups/shop-rg/providers/microsoft.dbformysql/flexibleservers/shop-mysql-prod</t>
   </si>
   <si>
-    <t>pay-mysql-prod</t>
-  </si>
-  <si>
-    <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a3/resourcegroups/pay-rg/providers/microsoft.dbformysql/flexibleservers/pay-mysql-prod</t>
-  </si>
-  <si>
     <t>pay-pg-prod</t>
   </si>
   <si>
@@ -948,6 +948,18 @@
     <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a5/resourcegroups/network-rg/providers/microsoft.network/virtualnetworkgateways/shared-vpn</t>
   </si>
   <si>
+    <t>pay-api-01</t>
+  </si>
+  <si>
+    <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a3/resourcegroups/pay-rg/providers/microsoft.compute/virtualmachines/pay-api-01</t>
+  </si>
+  <si>
+    <t>pay-api-02</t>
+  </si>
+  <si>
+    <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a3/resourcegroups/pay-rg/providers/microsoft.compute/virtualmachines/pay-api-02</t>
+  </si>
+  <si>
     <t>shop-web-01</t>
   </si>
   <si>
@@ -978,18 +990,6 @@
     <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a2/resourcegroups/shop-test-rg/providers/microsoft.compute/virtualmachines/shop-web-test-01</t>
   </si>
   <si>
-    <t>pay-api-01</t>
-  </si>
-  <si>
-    <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a3/resourcegroups/pay-rg/providers/microsoft.compute/virtualmachines/pay-api-01</t>
-  </si>
-  <si>
-    <t>pay-api-02</t>
-  </si>
-  <si>
-    <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a3/resourcegroups/pay-rg/providers/microsoft.compute/virtualmachines/pay-api-02</t>
-  </si>
-  <si>
     <t>data-worker-01</t>
   </si>
   <si>
@@ -1020,6 +1020,24 @@
     <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a3/resourcegroups/pay-rg/providers/microsoft.keyvault/vaults/pay-kv</t>
   </si>
   <si>
+    <t>data-etl-01-osdisk</t>
+  </si>
+  <si>
+    <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a4/resourcegroups/data-rg/providers/microsoft.compute/disks/data-etl-01-osdisk</t>
+  </si>
+  <si>
+    <t>pay-api-01-osdisk</t>
+  </si>
+  <si>
+    <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a3/resourcegroups/pay-rg/providers/microsoft.compute/disks/pay-api-01-osdisk</t>
+  </si>
+  <si>
+    <t>pay-api-02-osdisk</t>
+  </si>
+  <si>
+    <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a3/resourcegroups/pay-rg/providers/microsoft.compute/disks/pay-api-02-osdisk</t>
+  </si>
+  <si>
     <t>shop-batch-01-osdisk</t>
   </si>
   <si>
@@ -1060,24 +1078,6 @@
   </si>
   <si>
     <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a2/resourcegroups/shop-test-rg/providers/microsoft.compute/disks/shop-web-test-01-osdisk</t>
-  </si>
-  <si>
-    <t>pay-api-01-osdisk</t>
-  </si>
-  <si>
-    <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a3/resourcegroups/pay-rg/providers/microsoft.compute/disks/pay-api-01-osdisk</t>
-  </si>
-  <si>
-    <t>pay-api-02-osdisk</t>
-  </si>
-  <si>
-    <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a3/resourcegroups/pay-rg/providers/microsoft.compute/disks/pay-api-02-osdisk</t>
-  </si>
-  <si>
-    <t>data-etl-01-osdisk</t>
-  </si>
-  <si>
-    <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a4/resourcegroups/data-rg/providers/microsoft.compute/disks/data-etl-01-osdisk</t>
   </si>
   <si>
     <t>payreceipts</t>
@@ -2299,7 +2299,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CD0A-4D88-B8C3-17FAE29FD5C7}"/>
+              <c16:uniqueId val="{00000000-3E38-4F31-B00B-BDBE5934EEC3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2621,7 +2621,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-CD0A-4D88-B8C3-17FAE29FD5C7}"/>
+              <c16:uniqueId val="{00000001-3E38-4F31-B00B-BDBE5934EEC3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2919,7 +2919,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DD54-4197-BEE6-FDD0C113B966}"/>
+              <c16:uniqueId val="{00000000-2141-41D1-8994-89464ED33A2F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3076,7 +3076,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-DD54-4197-BEE6-FDD0C113B966}"/>
+              <c16:uniqueId val="{00000001-2141-41D1-8994-89464ED33A2F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3311,7 +3311,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-DD54-4197-BEE6-FDD0C113B966}"/>
+              <c16:uniqueId val="{00000002-2141-41D1-8994-89464ED33A2F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3478,7 +3478,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-845C-4C60-AE8F-EFFEB870872C}"/>
+              <c16:uniqueId val="{00000000-E285-47A6-9515-54C3DDFBC9A6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3566,7 +3566,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-845C-4C60-AE8F-EFFEB870872C}"/>
+              <c16:uniqueId val="{00000001-E285-47A6-9515-54C3DDFBC9A6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3690,7 +3690,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-C6D3-4861-81ED-0470CB27AB8A}"/>
+                <c16:uniqueId val="{00000001-4A57-4213-997D-1FEF5F5EFEC4}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3711,7 +3711,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-C6D3-4861-81ED-0470CB27AB8A}"/>
+                <c16:uniqueId val="{00000003-4A57-4213-997D-1FEF5F5EFEC4}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3732,7 +3732,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-C6D3-4861-81ED-0470CB27AB8A}"/>
+                <c16:uniqueId val="{00000005-4A57-4213-997D-1FEF5F5EFEC4}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3753,7 +3753,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-C6D3-4861-81ED-0470CB27AB8A}"/>
+                <c16:uniqueId val="{00000007-4A57-4213-997D-1FEF5F5EFEC4}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3763,7 +3763,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-C6D3-4861-81ED-0470CB27AB8A}"/>
+                <c16:uniqueId val="{00000009-4A57-4213-997D-1FEF5F5EFEC4}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3773,7 +3773,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-C6D3-4861-81ED-0470CB27AB8A}"/>
+                <c16:uniqueId val="{0000000B-4A57-4213-997D-1FEF5F5EFEC4}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3783,7 +3783,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-C6D3-4861-81ED-0470CB27AB8A}"/>
+                <c16:uniqueId val="{0000000D-4A57-4213-997D-1FEF5F5EFEC4}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3793,7 +3793,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-C6D3-4861-81ED-0470CB27AB8A}"/>
+                <c16:uniqueId val="{0000000F-4A57-4213-997D-1FEF5F5EFEC4}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3803,7 +3803,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-C6D3-4861-81ED-0470CB27AB8A}"/>
+                <c16:uniqueId val="{00000011-4A57-4213-997D-1FEF5F5EFEC4}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3813,7 +3813,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-C6D3-4861-81ED-0470CB27AB8A}"/>
+                <c16:uniqueId val="{00000013-4A57-4213-997D-1FEF5F5EFEC4}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3896,7 +3896,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000014-C6D3-4861-81ED-0470CB27AB8A}"/>
+              <c16:uniqueId val="{00000014-4A57-4213-997D-1FEF5F5EFEC4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4016,7 +4016,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-2D80-4B5F-B85A-67EFFC6519DF}"/>
+                <c16:uniqueId val="{00000001-A27C-463C-934F-C00A806942C6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4037,7 +4037,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-2D80-4B5F-B85A-67EFFC6519DF}"/>
+                <c16:uniqueId val="{00000003-A27C-463C-934F-C00A806942C6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4072,7 +4072,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-2D80-4B5F-B85A-67EFFC6519DF}"/>
+              <c16:uniqueId val="{00000004-A27C-463C-934F-C00A806942C6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5068,10 +5068,10 @@
     </row>
     <row r="9" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>264</v>
@@ -5088,10 +5088,10 @@
     </row>
     <row r="10" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>266</v>
@@ -5268,10 +5268,10 @@
     </row>
     <row r="19" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>282</v>
@@ -5288,10 +5288,10 @@
     </row>
     <row r="20" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>284</v>
@@ -5348,10 +5348,10 @@
     </row>
     <row r="23" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>290</v>
@@ -5368,10 +5368,10 @@
     </row>
     <row r="24" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>292</v>
@@ -5388,10 +5388,10 @@
     </row>
     <row r="25" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>294</v>
@@ -5506,12 +5506,12 @@
         <v>305</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="75" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>306</v>
@@ -5526,12 +5526,12 @@
         <v>307</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="75" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>308</v>
@@ -5546,12 +5546,12 @@
         <v>309</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="75" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>310</v>
@@ -5628,10 +5628,10 @@
     </row>
     <row r="37" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>318</v>
@@ -5646,12 +5646,12 @@
         <v>319</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="75" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>320</v>
@@ -5666,12 +5666,12 @@
         <v>321</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="75" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>322</v>
@@ -5686,12 +5686,12 @@
         <v>323</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="75" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>324</v>
@@ -7411,7 +7411,7 @@
         <v>246</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>466</v>
@@ -7450,7 +7450,7 @@
         <v>247</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>466</v>

--- a/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
+++ b/examples/sample-output/Contoso_Azure巡检报告_2026年10月/01_9月月度成本巡检报告.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30625"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-9n18lti6\2026-09\reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wez\AppData\Local\Temp\azinspect-sample-f6nzzhop\2026-09\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE65942-75F1-42C1-96EA-153F6F2AFF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214A0C3B-C445-4F4A-ABA5-C5814AFC3C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月度总览" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'10月费用预测'!$A$3:$I$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'9月资源费用'!$A$3:$F$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'9月资源费用'!$A$3:$F$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">Azure购买建议!$A$3:$J$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">RI与SP!$A$3:$I$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">业务组对比!$A$3:$H$7</definedName>
@@ -57,7 +57,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">服务对比!$A$3:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">每日费用!$A$3:$C$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">订阅对比!$A$3:$M$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">资源组对比!$A$3:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">资源组对比!$A$3:$F$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">预算检查!$A$3:$I$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'10月费用预测'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'9月资源费用'!$1:$3</definedName>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="576">
   <si>
     <t>示例客户：2026年9月成本巡检（对比8月）</t>
   </si>
@@ -174,7 +174,7 @@
     <t>数据查询时间</t>
   </si>
   <si>
-    <t>2026-10-29T21:12:04.445154+00:00</t>
+    <t>2026-10-30T02:43:30.729371+00:00</t>
   </si>
   <si>
     <t>完整月份费用按查询时结果列示</t>
@@ -651,7 +651,7 @@
     <t>日本东部（ja east）</t>
   </si>
   <si>
-    <t>Azure Database for PostgreSQL +573；Log Analytics +375；Virtual Machines -188</t>
+    <t>Azure Database for PostgreSQL +573；Log Analytics +375；Virtual Machines -194</t>
   </si>
   <si>
     <t>美国东部（us east）</t>
@@ -708,13 +708,13 @@
     <t>日均用量变化 USD +84；天数差异 USD -14；新增计量或资源 USD +12；新增 1 个资源（按账单拆分，业务原因待确认）</t>
   </si>
   <si>
-    <t>日均用量变化 USD +11；天数差异 USD -7（按账单拆分，业务原因待确认）</t>
+    <t>日均用量变化 USD +11；天数差异 USD -8（按账单拆分，业务原因待确认）</t>
   </si>
   <si>
     <t>shop-web-test-02 于 8 月 20 日释放，9 月不再计费</t>
   </si>
   <si>
-    <t>天数差异 USD -51（按账单拆分，业务原因待确认）</t>
+    <t>天数差异 USD -57（按账单拆分，业务原因待确认）</t>
   </si>
   <si>
     <t>天数差异 USD -42（按账单拆分，业务原因待确认）</t>
@@ -852,6 +852,9 @@
     <t>network-rg</t>
   </si>
   <si>
+    <t>shop-net-rg</t>
+  </si>
+  <si>
     <t>9月资源级费用</t>
   </si>
   <si>
@@ -960,6 +963,12 @@
     <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a3/resourcegroups/pay-rg/providers/microsoft.compute/virtualmachines/pay-api-02</t>
   </si>
   <si>
+    <t>edge-fw-01</t>
+  </si>
+  <si>
+    <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a1/resourcegroups/shop-net-rg/providers/microsoft.compute/virtualmachines/edge-fw-01</t>
+  </si>
+  <si>
     <t>shop-web-01</t>
   </si>
   <si>
@@ -1038,6 +1047,12 @@
     <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a3/resourcegroups/pay-rg/providers/microsoft.compute/disks/pay-api-02-osdisk</t>
   </si>
   <si>
+    <t>edge-fw-01-osdisk</t>
+  </si>
+  <si>
+    <t>/subscriptions/5a1e0c01-1111-4c2a-9a10-0000000000a1/resourcegroups/shop-net-rg/providers/microsoft.compute/disks/edge-fw-01-osdisk</t>
+  </si>
+  <si>
     <t>shop-batch-01-osdisk</t>
   </si>
   <si>
@@ -1236,7 +1251,7 @@
     <t>2026-12-15</t>
   </si>
   <si>
-    <t>47 天后到期，未设置自动续订</t>
+    <t>46 天后到期，未设置自动续订</t>
   </si>
   <si>
     <t>Azure 基于过去 30 天用量的 RI/SP 购买建议</t>
@@ -1392,7 +1407,7 @@
     <t>长期稳定计算、数据库、缓存及可预留存储费用</t>
   </si>
   <si>
-    <t>9月分摊费用中 8.3% 由 RI/SP 覆盖；现有 2 个预留、1 个节省计划，其中 1 个近 30 天未用满，1 个即将到期；Azure 基于过去 30 天用量估算，购买 1 年期预留实例约节省 USD 128.62，购买 1 年期节省计划约节省 USD 188.60（每 30 天，按当前用量、未计入降配；预留实例和节省计划覆盖同一部分用量，只能选其一，3 年期方案见 Excel）</t>
+    <t>9月分摊费用中 7.8% 由 RI/SP 覆盖；现有 2 个预留、1 个节省计划，其中 1 个近 30 天未用满，1 个即将到期；Azure 基于过去 30 天用量估算，购买 1 年期预留实例约节省 USD 128.62，购买 1 年期节省计划约节省 USD 188.60（每 30 天，按当前用量、未计入降配；预留实例和节省计划覆盖同一部分用量，只能选其一，3 年期方案见 Excel）</t>
   </si>
   <si>
     <t>先确定调整后的长期用量，再比较适用的1年/3年RI和SP；不要按全年满配估算直接采购</t>
@@ -2201,97 +2216,97 @@
                 <c:formatCode>#,##0.00;\(#,##0.00\);"-"</c:formatCode>
                 <c:ptCount val="61"/>
                 <c:pt idx="0">
-                  <c:v>461.14850000000001</c:v>
+                  <c:v>467.75749999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>455.50380000000001</c:v>
+                  <c:v>462.11279999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>563.57100000000003</c:v>
+                  <c:v>570.17999999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>550.92129999999997</c:v>
+                  <c:v>557.53030000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>556.50670000000002</c:v>
+                  <c:v>563.11569999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>543.50699999999995</c:v>
+                  <c:v>550.11599999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>554.72490000000005</c:v>
+                  <c:v>561.33389999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>463.85899999999998</c:v>
+                  <c:v>470.46800000000002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>453.40100000000001</c:v>
+                  <c:v>460.01</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>555.22130000000004</c:v>
+                  <c:v>561.83029999999997</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>551.94960000000003</c:v>
+                  <c:v>558.55859999999996</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>553.93650000000002</c:v>
+                  <c:v>560.54550000000006</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>545.68809999999996</c:v>
+                  <c:v>552.2971</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>559.62130000000002</c:v>
+                  <c:v>566.23029999999994</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>456.20760000000001</c:v>
+                  <c:v>462.81659999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>464.64600000000002</c:v>
+                  <c:v>471.255</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>563.87400000000002</c:v>
+                  <c:v>570.48299999999995</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>546.76220000000001</c:v>
+                  <c:v>553.37120000000004</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>544.72749999999996</c:v>
+                  <c:v>551.3365</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>555.17280000000005</c:v>
+                  <c:v>561.78179999999998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>555.51290000000006</c:v>
+                  <c:v>562.12189999999998</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>456.7817</c:v>
+                  <c:v>463.39069999999998</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>452.0933</c:v>
+                  <c:v>458.70229999999998</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>555.11469999999997</c:v>
+                  <c:v>561.72370000000001</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>558.48099999999999</c:v>
+                  <c:v>565.09</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>553.61919999999998</c:v>
+                  <c:v>560.22820000000002</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>551.22130000000004</c:v>
+                  <c:v>557.83029999999997</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>545.29280000000006</c:v>
+                  <c:v>551.90179999999998</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>460.24250000000001</c:v>
+                  <c:v>466.85149999999999</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>462.1037</c:v>
+                  <c:v>468.71269999999998</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>544.94809999999995</c:v>
+                  <c:v>551.55709999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2299,7 +2314,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3E38-4F31-B00B-BDBE5934EEC3}"/>
+              <c16:uniqueId val="{00000000-6D89-485C-BA60-E015893A63B8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2526,94 +2541,94 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="61"/>
                 <c:pt idx="31" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>553.49680000000001</c:v>
+                  <c:v>560.10580000000004</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>559.88810000000001</c:v>
+                  <c:v>566.49710000000005</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>555.70730000000003</c:v>
+                  <c:v>562.31629999999996</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>571.92809999999997</c:v>
+                  <c:v>578.53710000000001</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>459.32940000000002</c:v>
+                  <c:v>465.9384</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>466.36869999999999</c:v>
+                  <c:v>472.97770000000003</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>565.64239999999995</c:v>
+                  <c:v>572.25139999999999</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>586.09050000000002</c:v>
+                  <c:v>592.69950000000006</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>597.45690000000002</c:v>
+                  <c:v>604.06590000000006</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>598.43500000000006</c:v>
+                  <c:v>605.04399999999998</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>592.74289999999996</c:v>
+                  <c:v>599.3519</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>497.28289999999998</c:v>
+                  <c:v>503.89190000000002</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>502.35759999999999</c:v>
+                  <c:v>508.96660000000003</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>599.6875</c:v>
+                  <c:v>606.29650000000004</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>636.48860000000002</c:v>
+                  <c:v>643.09760000000006</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>617.72800000000007</c:v>
+                  <c:v>624.33699999999999</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>631.40219999999999</c:v>
+                  <c:v>638.01120000000003</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>632.36149999999998</c:v>
+                  <c:v>638.97050000000002</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>524.0258</c:v>
+                  <c:v>530.63480000000004</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>520.97580000000005</c:v>
+                  <c:v>527.58479999999997</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>621.6232</c:v>
+                  <c:v>628.23220000000003</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>619.85619999999994</c:v>
+                  <c:v>626.46519999999998</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>628.68520000000001</c:v>
+                  <c:v>635.29420000000005</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>627.81989999999996</c:v>
+                  <c:v>634.4289</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>640.27930000000003</c:v>
+                  <c:v>646.88829999999996</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>522.6558</c:v>
+                  <c:v>529.26480000000004</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>525.76089999999999</c:v>
+                  <c:v>532.36990000000003</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>637.30960000000005</c:v>
+                  <c:v>643.91859999999997</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>622.77660000000003</c:v>
+                  <c:v>629.38560000000007</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>634.77980000000002</c:v>
+                  <c:v>641.38880000000006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2621,7 +2636,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3E38-4F31-B00B-BDBE5934EEC3}"/>
+              <c16:uniqueId val="{00000001-6D89-485C-BA60-E015893A63B8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2836,82 +2851,82 @@
                 <c:formatCode>#,##0.00;\(#,##0.00\);"-"</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>625.02160000000003</c:v>
+                  <c:v>631.63060000000007</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>625.58620000000008</c:v>
+                  <c:v>632.19520000000011</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>522.5200000000001</c:v>
+                  <c:v>529.12900000000013</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>522.9393</c:v>
+                  <c:v>529.54830000000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>634.13270000000011</c:v>
+                  <c:v>640.74170000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>627.79370000000006</c:v>
+                  <c:v>634.4027000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>633.00520000000006</c:v>
+                  <c:v>639.61419999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>630.03070000000002</c:v>
+                  <c:v>636.63970000000006</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>631.37400000000002</c:v>
+                  <c:v>637.98300000000006</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>533.1069</c:v>
+                  <c:v>539.71590000000003</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>521.82230000000004</c:v>
+                  <c:v>528.43130000000008</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>636.70240000000013</c:v>
+                  <c:v>643.31140000000005</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>639.46900000000005</c:v>
+                  <c:v>646.07799999999997</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>635.03280000000007</c:v>
+                  <c:v>641.64179999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>643.47460000000001</c:v>
+                  <c:v>650.08360000000005</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>636.91560000000004</c:v>
+                  <c:v>643.52460000000008</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>524.8886</c:v>
+                  <c:v>531.49760000000003</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>529.5489</c:v>
+                  <c:v>536.15790000000004</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>627.92690000000005</c:v>
+                  <c:v>634.53590000000008</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>642.00540000000001</c:v>
+                  <c:v>648.61440000000005</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>628.89940000000001</c:v>
+                  <c:v>635.50840000000005</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>629.02320000000009</c:v>
+                  <c:v>635.63220000000001</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>644.95950000000005</c:v>
+                  <c:v>651.56850000000009</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>532.54500000000007</c:v>
+                  <c:v>539.154</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>535.88990000000013</c:v>
+                  <c:v>542.49890000000005</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>631.09440000000006</c:v>
+                  <c:v>637.7034000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2919,7 +2934,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2141-41D1-8994-89464ED33A2F}"/>
+              <c16:uniqueId val="{00000000-2F44-46E0-A3EF-C5FE15629F80}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3056,19 +3071,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="26" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>606.34525700000006</c:v>
+                  <c:v>612.9542570000001</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>606.34525700000006</c:v>
+                  <c:v>612.9542570000001</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>606.34525700000006</c:v>
+                  <c:v>612.9542570000001</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>606.34525700000006</c:v>
+                  <c:v>612.9542570000001</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;">
-                  <c:v>424.44168000000002</c:v>
+                  <c:v>429.06797999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3076,7 +3091,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-2141-41D1-8994-89464ED33A2F}"/>
+              <c16:uniqueId val="{00000001-2F44-46E0-A3EF-C5FE15629F80}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3213,97 +3228,97 @@
                 <c:formatCode>#,##0.00;\(#,##0.00\);"-"</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>578.36475000000007</c:v>
+                  <c:v>584.97375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3311,7 +3326,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-2141-41D1-8994-89464ED33A2F}"/>
+              <c16:uniqueId val="{00000002-2F44-46E0-A3EF-C5FE15629F80}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3447,7 +3462,7 @@
                 <c:formatCode>#,##0.00;\(#,##0.00\);"-"</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>9893.9446000000007</c:v>
+                  <c:v>10098.8236</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>4757.6990999999998</c:v>
@@ -3478,7 +3493,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E285-47A6-9515-54C3DDFBC9A6}"/>
+              <c16:uniqueId val="{00000000-7EF9-4C2C-8286-76FF94C7984F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3535,7 +3550,7 @@
                 <c:formatCode>#,##0.00;\(#,##0.00\);"-"</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>9986.268</c:v>
+                  <c:v>10184.538</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>5295.8909000000003</c:v>
@@ -3566,7 +3581,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E285-47A6-9515-54C3DDFBC9A6}"/>
+              <c16:uniqueId val="{00000001-7EF9-4C2C-8286-76FF94C7984F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3690,7 +3705,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-4A57-4213-997D-1FEF5F5EFEC4}"/>
+                <c16:uniqueId val="{00000001-900D-4268-89B9-F800F9CF77CC}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3711,7 +3726,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-4A57-4213-997D-1FEF5F5EFEC4}"/>
+                <c16:uniqueId val="{00000003-900D-4268-89B9-F800F9CF77CC}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3732,7 +3747,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-4A57-4213-997D-1FEF5F5EFEC4}"/>
+                <c16:uniqueId val="{00000005-900D-4268-89B9-F800F9CF77CC}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3753,7 +3768,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-4A57-4213-997D-1FEF5F5EFEC4}"/>
+                <c16:uniqueId val="{00000007-900D-4268-89B9-F800F9CF77CC}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3763,7 +3778,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-4A57-4213-997D-1FEF5F5EFEC4}"/>
+                <c16:uniqueId val="{00000009-900D-4268-89B9-F800F9CF77CC}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3773,7 +3788,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-4A57-4213-997D-1FEF5F5EFEC4}"/>
+                <c16:uniqueId val="{0000000B-900D-4268-89B9-F800F9CF77CC}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3783,7 +3798,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-4A57-4213-997D-1FEF5F5EFEC4}"/>
+                <c16:uniqueId val="{0000000D-900D-4268-89B9-F800F9CF77CC}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3793,7 +3808,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-4A57-4213-997D-1FEF5F5EFEC4}"/>
+                <c16:uniqueId val="{0000000F-900D-4268-89B9-F800F9CF77CC}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3803,7 +3818,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-4A57-4213-997D-1FEF5F5EFEC4}"/>
+                <c16:uniqueId val="{00000011-900D-4268-89B9-F800F9CF77CC}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3813,7 +3828,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-4A57-4213-997D-1FEF5F5EFEC4}"/>
+                <c16:uniqueId val="{00000013-900D-4268-89B9-F800F9CF77CC}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3871,7 +3886,7 @@
                   <c:v>348.63400000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>71.957000000000107</c:v>
+                  <c:v>71.299999999999955</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>-51.300000000000182</c:v>
@@ -3880,7 +3895,7 @@
                   <c:v>-41.319600000000257</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-25.199999999999822</c:v>
+                  <c:v>-31.15200000000004</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>-13.19999999999999</c:v>
@@ -3896,7 +3911,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000014-4A57-4213-997D-1FEF5F5EFEC4}"/>
+              <c16:uniqueId val="{00000014-900D-4268-89B9-F800F9CF77CC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4016,7 +4031,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-A27C-463C-934F-C00A806942C6}"/>
+                <c16:uniqueId val="{00000001-7373-4CEA-AB94-2C1384E51FAB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4037,7 +4052,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-A27C-463C-934F-C00A806942C6}"/>
+                <c16:uniqueId val="{00000003-7373-4CEA-AB94-2C1384E51FAB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4062,7 +4077,7 @@
                 <c:formatCode>#,##0.00;\(#,##0.00\);"-"</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>616.38940000000002</c:v>
+                  <c:v>609.78039999999964</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>538.19180000000051</c:v>
@@ -4072,7 +4087,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-A27C-463C-934F-C00A806942C6}"/>
+              <c16:uniqueId val="{00000004-7373-4CEA-AB94-2C1384E51FAB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4630,7 +4645,7 @@
       </c>
       <c r="B5" s="6">
         <f>订阅对比!D4+订阅对比!D5+订阅对比!D6+订阅对比!D7+订阅对比!D8</f>
-        <v>17350.942500000001</v>
+        <v>17549.212500000001</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>8</v>
@@ -4642,7 +4657,7 @@
       </c>
       <c r="B6" s="7">
         <f>订阅对比!C4+订阅对比!C5+订阅对比!C6+订阅对比!C7+订阅对比!C8</f>
-        <v>16196.361299999999</v>
+        <v>16401.240300000001</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>10</v>
@@ -4654,7 +4669,7 @@
       </c>
       <c r="B7" s="8">
         <f>B5-B6</f>
-        <v>1154.5812000000024</v>
+        <v>1147.9722000000002</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>12</v>
@@ -4666,7 +4681,7 @@
       </c>
       <c r="B8" s="9">
         <f>B5/B6-1</f>
-        <v>7.1286456174573187E-2</v>
+        <v>6.9993011443165054E-2</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>14</v>
@@ -4678,7 +4693,7 @@
       </c>
       <c r="B9" s="8">
         <f>B5/30</f>
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>16</v>
@@ -4690,7 +4705,7 @@
       </c>
       <c r="B10" s="10">
         <f>B6/31</f>
-        <v>522.4632677419354</v>
+        <v>529.07226774193555</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>18</v>
@@ -4702,7 +4717,7 @@
       </c>
       <c r="B11" s="11">
         <f>B9/B10-1</f>
-        <v>0.10699600471372572</v>
+        <v>0.10565944515793713</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>20</v>
@@ -4713,7 +4728,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="5">
-        <v>17350.942500000001</v>
+        <v>17549.212500000001</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>22</v>
@@ -4735,7 +4750,7 @@
         <v>26</v>
       </c>
       <c r="B14" s="5">
-        <v>18475.530908000001</v>
+        <v>18678.427208000001</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>27</v>
@@ -4754,7 +4769,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -4815,7 +4830,7 @@
         <v>5295.8909000000003</v>
       </c>
       <c r="E4" s="10">
-        <f>D4-C4</f>
+        <f t="shared" ref="E4:E9" si="0">D4-C4</f>
         <v>538.19180000000051</v>
       </c>
       <c r="F4" s="5">
@@ -4836,7 +4851,7 @@
         <v>1717.7836</v>
       </c>
       <c r="E5" s="8">
-        <f>D5-C5</f>
+        <f t="shared" si="0"/>
         <v>535.76600000000008</v>
       </c>
       <c r="F5" s="12">
@@ -4857,7 +4872,7 @@
         <v>9664.9979999999996</v>
       </c>
       <c r="E6" s="10">
-        <f>D6-C6</f>
+        <f t="shared" si="0"/>
         <v>235.21240000000034</v>
       </c>
       <c r="F6" s="5">
@@ -4878,7 +4893,7 @@
         <v>321.27</v>
       </c>
       <c r="E7" s="8">
-        <f>D7-C7</f>
+        <f t="shared" si="0"/>
         <v>-142.88900000000001</v>
       </c>
       <c r="F7" s="12">
@@ -4899,15 +4914,36 @@
         <v>351</v>
       </c>
       <c r="E8" s="10">
-        <f>D8-C8</f>
+        <f t="shared" si="0"/>
         <v>-11.699999999999989</v>
       </c>
       <c r="F8" s="5">
         <v>-3.2258064516128997E-2</v>
       </c>
     </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C9" s="12">
+        <v>204.87899999999999</v>
+      </c>
+      <c r="D9" s="12">
+        <v>198.27</v>
+      </c>
+      <c r="E9" s="8">
+        <f t="shared" si="0"/>
+        <v>-6.6089999999999804</v>
+      </c>
+      <c r="F9" s="12">
+        <v>-3.2258064516128893E-2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:F8" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
+  <autoFilter ref="A3:F9" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -4919,7 +4955,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -4928,7 +4964,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -4938,7 +4974,7 @@
     </row>
     <row r="2" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -4954,7 +4990,7 @@
         <v>244</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>138</v>
@@ -4963,7 +4999,7 @@
         <v>32</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -4974,7 +5010,7 @@
         <v>247</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>142</v>
@@ -4983,7 +5019,7 @@
         <v>3556.306</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -4994,7 +5030,7 @@
         <v>247</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>145</v>
@@ -5003,7 +5039,7 @@
         <v>2822.6995999999999</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5014,7 +5050,7 @@
         <v>245</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>142</v>
@@ -5023,7 +5059,7 @@
         <v>1815.528</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5034,7 +5070,7 @@
         <v>245</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>140</v>
@@ -5043,7 +5079,7 @@
         <v>1245</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5054,7 +5090,7 @@
         <v>245</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>141</v>
@@ -5063,7 +5099,7 @@
         <v>1187.5338999999999</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5074,7 +5110,7 @@
         <v>246</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>144</v>
@@ -5083,7 +5119,7 @@
         <v>708</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5094,7 +5130,7 @@
         <v>247</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>144</v>
@@ -5103,7 +5139,7 @@
         <v>708</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5114,7 +5150,7 @@
         <v>246</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>140</v>
@@ -5123,7 +5159,7 @@
         <v>572.70000000000005</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5134,7 +5170,7 @@
         <v>245</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>143</v>
@@ -5143,7 +5179,7 @@
         <v>477.65199999999999</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5154,7 +5190,7 @@
         <v>247</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>146</v>
@@ -5163,7 +5199,7 @@
         <v>468</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="75" x14ac:dyDescent="0.35">
@@ -5174,7 +5210,7 @@
         <v>247</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>147</v>
@@ -5183,7 +5219,7 @@
         <v>396</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5194,7 +5230,7 @@
         <v>245</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>146</v>
@@ -5203,7 +5239,7 @@
         <v>362.88</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5214,7 +5250,7 @@
         <v>247</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>146</v>
@@ -5223,7 +5259,7 @@
         <v>357.12</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5234,7 +5270,7 @@
         <v>247</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>148</v>
@@ -5243,7 +5279,7 @@
         <v>354</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5254,7 +5290,7 @@
         <v>249</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>149</v>
@@ -5263,7 +5299,7 @@
         <v>351</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5274,7 +5310,7 @@
         <v>246</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>146</v>
@@ -5283,7 +5319,7 @@
         <v>178.56</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5294,7 +5330,7 @@
         <v>246</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>146</v>
@@ -5303,7 +5339,7 @@
         <v>178.56</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5311,10 +5347,10 @@
         <v>159</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>146</v>
@@ -5323,7 +5359,7 @@
         <v>178.56</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5334,7 +5370,7 @@
         <v>247</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>146</v>
@@ -5343,7 +5379,7 @@
         <v>178.56</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5354,7 +5390,7 @@
         <v>247</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>146</v>
@@ -5363,7 +5399,7 @@
         <v>178.56</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5374,7 +5410,7 @@
         <v>247</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>146</v>
@@ -5383,18 +5419,18 @@
         <v>178.56</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>146</v>
@@ -5403,67 +5439,67 @@
         <v>178.56</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>146</v>
       </c>
       <c r="E26" s="5">
-        <v>175.10400000000001</v>
+        <v>178.56</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E27" s="12">
-        <v>123</v>
+        <v>175.10400000000001</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E28" s="5">
-        <v>98.372399999999999</v>
+        <v>123</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5474,67 +5510,67 @@
         <v>247</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E29" s="12">
+        <v>98.372399999999999</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E30" s="5">
         <v>72</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="75" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="E30" s="5">
-        <v>27</v>
-      </c>
       <c r="F30" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="75" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="E31" s="12">
-        <v>19.71</v>
+        <v>27</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="75" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>143</v>
@@ -5543,7 +5579,7 @@
         <v>19.71</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="75" x14ac:dyDescent="0.35">
@@ -5554,7 +5590,7 @@
         <v>246</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>143</v>
@@ -5563,18 +5599,18 @@
         <v>19.71</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="75" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>143</v>
@@ -5583,18 +5619,18 @@
         <v>19.71</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="75" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>159</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>143</v>
@@ -5603,7 +5639,7 @@
         <v>19.71</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5614,7 +5650,7 @@
         <v>247</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>143</v>
@@ -5623,7 +5659,7 @@
         <v>19.71</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5634,7 +5670,7 @@
         <v>247</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>143</v>
@@ -5643,7 +5679,7 @@
         <v>19.71</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5654,7 +5690,7 @@
         <v>247</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>143</v>
@@ -5663,7 +5699,7 @@
         <v>19.71</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
@@ -5674,7 +5710,7 @@
         <v>247</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>143</v>
@@ -5683,18 +5719,18 @@
         <v>19.71</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>143</v>
@@ -5703,51 +5739,91 @@
         <v>19.71</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>143</v>
       </c>
       <c r="E41" s="12">
-        <v>13.5436</v>
+        <v>19.71</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>143</v>
       </c>
       <c r="E42" s="5">
+        <v>19.71</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E43" s="12">
+        <v>13.5436</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E44" s="5">
         <v>12.483000000000001</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>329</v>
+      <c r="F44" s="4" t="s">
+        <v>334</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F42" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
+  <autoFilter ref="A3:F44" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -5768,21 +5844,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
     </row>
     <row r="2" spans="1:3" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
     </row>
     <row r="3" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>31</v>
@@ -5796,10 +5872,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="5">
-        <v>461.14850000000001</v>
+        <v>467.75749999999999</v>
       </c>
       <c r="C4" s="5">
-        <v>553.49680000000001</v>
+        <v>560.10580000000004</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -5807,10 +5883,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="12">
-        <v>455.50380000000001</v>
+        <v>462.11279999999999</v>
       </c>
       <c r="C5" s="12">
-        <v>559.88810000000001</v>
+        <v>566.49710000000005</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -5818,10 +5894,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="5">
-        <v>563.57100000000003</v>
+        <v>570.17999999999995</v>
       </c>
       <c r="C6" s="5">
-        <v>555.70730000000003</v>
+        <v>562.31629999999996</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -5829,10 +5905,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="12">
-        <v>550.92129999999997</v>
+        <v>557.53030000000001</v>
       </c>
       <c r="C7" s="12">
-        <v>571.92809999999997</v>
+        <v>578.53710000000001</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -5840,10 +5916,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="5">
-        <v>556.50670000000002</v>
+        <v>563.11569999999995</v>
       </c>
       <c r="C8" s="5">
-        <v>459.32940000000002</v>
+        <v>465.9384</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -5851,10 +5927,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="12">
-        <v>543.50699999999995</v>
+        <v>550.11599999999999</v>
       </c>
       <c r="C9" s="12">
-        <v>466.36869999999999</v>
+        <v>472.97770000000003</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -5862,10 +5938,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="5">
-        <v>554.72490000000005</v>
+        <v>561.33389999999997</v>
       </c>
       <c r="C10" s="5">
-        <v>565.64239999999995</v>
+        <v>572.25139999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -5873,10 +5949,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="12">
-        <v>463.85899999999998</v>
+        <v>470.46800000000002</v>
       </c>
       <c r="C11" s="12">
-        <v>586.09050000000002</v>
+        <v>592.69950000000006</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -5884,10 +5960,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="5">
-        <v>453.40100000000001</v>
+        <v>460.01</v>
       </c>
       <c r="C12" s="5">
-        <v>597.45690000000002</v>
+        <v>604.06590000000006</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -5895,10 +5971,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="12">
-        <v>555.22130000000004</v>
+        <v>561.83029999999997</v>
       </c>
       <c r="C13" s="12">
-        <v>598.43500000000006</v>
+        <v>605.04399999999998</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -5906,10 +5982,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="5">
-        <v>551.94960000000003</v>
+        <v>558.55859999999996</v>
       </c>
       <c r="C14" s="5">
-        <v>592.74289999999996</v>
+        <v>599.3519</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -5917,10 +5993,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="12">
-        <v>553.93650000000002</v>
+        <v>560.54550000000006</v>
       </c>
       <c r="C15" s="12">
-        <v>497.28289999999998</v>
+        <v>503.89190000000002</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -5928,10 +6004,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="5">
-        <v>545.68809999999996</v>
+        <v>552.2971</v>
       </c>
       <c r="C16" s="5">
-        <v>502.35759999999999</v>
+        <v>508.96660000000003</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -5939,10 +6015,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="12">
-        <v>559.62130000000002</v>
+        <v>566.23029999999994</v>
       </c>
       <c r="C17" s="12">
-        <v>599.6875</v>
+        <v>606.29650000000004</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -5950,10 +6026,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="5">
-        <v>456.20760000000001</v>
+        <v>462.81659999999999</v>
       </c>
       <c r="C18" s="5">
-        <v>636.48860000000002</v>
+        <v>643.09760000000006</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -5961,10 +6037,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="12">
-        <v>464.64600000000002</v>
+        <v>471.255</v>
       </c>
       <c r="C19" s="12">
-        <v>617.72800000000007</v>
+        <v>624.33699999999999</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -5972,10 +6048,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="5">
-        <v>563.87400000000002</v>
+        <v>570.48299999999995</v>
       </c>
       <c r="C20" s="5">
-        <v>631.40219999999999</v>
+        <v>638.01120000000003</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -5983,10 +6059,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="12">
-        <v>546.76220000000001</v>
+        <v>553.37120000000004</v>
       </c>
       <c r="C21" s="12">
-        <v>632.36149999999998</v>
+        <v>638.97050000000002</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -5994,10 +6070,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="5">
-        <v>544.72749999999996</v>
+        <v>551.3365</v>
       </c>
       <c r="C22" s="5">
-        <v>524.0258</v>
+        <v>530.63480000000004</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -6005,10 +6081,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="12">
-        <v>555.17280000000005</v>
+        <v>561.78179999999998</v>
       </c>
       <c r="C23" s="12">
-        <v>520.97580000000005</v>
+        <v>527.58479999999997</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -6016,10 +6092,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="5">
-        <v>555.51290000000006</v>
+        <v>562.12189999999998</v>
       </c>
       <c r="C24" s="5">
-        <v>621.6232</v>
+        <v>628.23220000000003</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -6027,10 +6103,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="12">
-        <v>456.7817</v>
+        <v>463.39069999999998</v>
       </c>
       <c r="C25" s="12">
-        <v>619.85619999999994</v>
+        <v>626.46519999999998</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -6038,10 +6114,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="5">
-        <v>452.0933</v>
+        <v>458.70229999999998</v>
       </c>
       <c r="C26" s="5">
-        <v>628.68520000000001</v>
+        <v>635.29420000000005</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -6049,10 +6125,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="12">
-        <v>555.11469999999997</v>
+        <v>561.72370000000001</v>
       </c>
       <c r="C27" s="12">
-        <v>627.81989999999996</v>
+        <v>634.4289</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -6060,10 +6136,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="5">
-        <v>558.48099999999999</v>
+        <v>565.09</v>
       </c>
       <c r="C28" s="5">
-        <v>640.27930000000003</v>
+        <v>646.88829999999996</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -6071,10 +6147,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="12">
-        <v>553.61919999999998</v>
+        <v>560.22820000000002</v>
       </c>
       <c r="C29" s="12">
-        <v>522.6558</v>
+        <v>529.26480000000004</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -6082,10 +6158,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="5">
-        <v>551.22130000000004</v>
+        <v>557.83029999999997</v>
       </c>
       <c r="C30" s="5">
-        <v>525.76089999999999</v>
+        <v>532.36990000000003</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -6093,10 +6169,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="12">
-        <v>545.29280000000006</v>
+        <v>551.90179999999998</v>
       </c>
       <c r="C31" s="12">
-        <v>637.30960000000005</v>
+        <v>643.91859999999997</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
@@ -6104,10 +6180,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="5">
-        <v>460.24250000000001</v>
+        <v>466.85149999999999</v>
       </c>
       <c r="C32" s="5">
-        <v>622.77660000000003</v>
+        <v>629.38560000000007</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
@@ -6115,10 +6191,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="12">
-        <v>462.1037</v>
+        <v>468.71269999999998</v>
       </c>
       <c r="C33" s="12">
-        <v>634.77980000000002</v>
+        <v>641.38880000000006</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
@@ -6126,7 +6202,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="5">
-        <v>544.94809999999995</v>
+        <v>551.55709999999999</v>
       </c>
       <c r="C34" s="4"/>
     </row>
@@ -6152,7 +6228,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -6165,7 +6241,7 @@
     </row>
     <row r="2" spans="1:9" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -6184,22 +6260,22 @@
         <v>154</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>4</v>
@@ -6213,21 +6289,21 @@
         <v>159</v>
       </c>
       <c r="C4" s="5">
-        <v>8573.2159000000011</v>
+        <v>8745.0499</v>
       </c>
       <c r="D4" s="5">
-        <v>1569.0330959999999</v>
+        <v>1600.0953959999999</v>
       </c>
       <c r="E4" s="10">
         <f>C4+D4</f>
-        <v>10142.248996</v>
+        <v>10345.145296000001</v>
       </c>
       <c r="F4" s="5">
-        <v>9664.9979999999996</v>
+        <v>9863.268</v>
       </c>
       <c r="G4" s="9">
         <f t="shared" ref="G4:G9" si="0">(E4/31)/(F4/30)-1</f>
-        <v>1.5528370885166121E-2</v>
+        <v>1.5021687701571418E-2</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -6345,34 +6421,34 @@
         <v>186</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C9" s="8">
         <f>SUM(C4:C8)</f>
-        <v>15625.708200000001</v>
+        <v>15797.5422</v>
       </c>
       <c r="D9" s="8">
         <f>SUM(D4:D8)</f>
-        <v>2849.8227079999997</v>
+        <v>2880.8850079999997</v>
       </c>
       <c r="E9" s="8">
         <f>SUM(E4:E8)</f>
-        <v>18475.530907999997</v>
+        <v>18678.427207999997</v>
       </c>
       <c r="F9" s="8">
         <f>SUM(F4:F8)</f>
-        <v>17350.942500000001</v>
+        <v>17549.212500000001</v>
       </c>
       <c r="G9" s="11">
         <f t="shared" si="0"/>
-        <v>3.0465407858967675E-2</v>
+        <v>3.0011876491011558E-2</v>
       </c>
       <c r="H9" s="8">
         <f>SUM(H4:H8)</f>
         <v>0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -6397,32 +6473,32 @@
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
     </row>
     <row r="2" spans="1:3" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
     </row>
     <row r="3" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>142</v>
@@ -6433,7 +6509,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>145</v>
@@ -6444,18 +6520,18 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>146</v>
       </c>
       <c r="C6" s="5">
-        <v>2613.0239999999999</v>
+        <v>2791.5839999999998</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="25" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>140</v>
@@ -6466,7 +6542,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>144</v>
@@ -6477,7 +6553,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>141</v>
@@ -6488,18 +6564,18 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>143</v>
       </c>
       <c r="C10" s="5">
-        <v>799.15100000000007</v>
+        <v>818.86099999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>147</v>
@@ -6510,7 +6586,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>148</v>
@@ -6521,7 +6597,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>149</v>
@@ -6532,7 +6608,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>176</v>
@@ -6543,7 +6619,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>177</v>
@@ -6554,32 +6630,32 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C16" s="5">
-        <v>17350.942500000001</v>
+        <v>17549.212500000001</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C17" s="12">
-        <v>2357.2800000000002</v>
+        <v>2535.84</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C18" s="5">
         <v>214.28</v>
@@ -6607,7 +6683,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -6620,7 +6696,7 @@
     </row>
     <row r="2" spans="1:9" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -6633,48 +6709,48 @@
     </row>
     <row r="3" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="F4" s="5">
         <v>99</v>
@@ -6683,27 +6759,27 @@
         <v>98.5</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="F5" s="12">
         <v>0</v>
@@ -6712,27 +6788,27 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>371</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>366</v>
       </c>
       <c r="F6" s="5">
         <v>99.6</v>
@@ -6741,10 +6817,10 @@
         <v>99.2</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -6769,7 +6845,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -6783,7 +6859,7 @@
     </row>
     <row r="2" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -6797,54 +6873,54 @@
     </row>
     <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>154</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>150</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>164</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -6861,22 +6937,22 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="G5" s="12">
         <v>2</v>
@@ -6893,20 +6969,20 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>159</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="G6" s="5">
         <v>0.95</v>
@@ -6948,7 +7024,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -6964,7 +7040,7 @@
     </row>
     <row r="2" spans="1:12" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -6980,64 +7056,64 @@
     </row>
     <row r="3" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
@@ -7046,26 +7122,26 @@
     </row>
     <row r="5" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -7074,26 +7150,26 @@
     </row>
     <row r="6" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -7102,26 +7178,26 @@
     </row>
     <row r="7" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -7130,28 +7206,28 @@
     </row>
     <row r="8" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="E8" s="5">
         <v>760.51400000000001</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
@@ -7160,26 +7236,26 @@
     </row>
     <row r="9" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -7188,26 +7264,26 @@
     </row>
     <row r="10" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -7216,26 +7292,26 @@
     </row>
     <row r="11" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -7244,26 +7320,26 @@
     </row>
     <row r="12" spans="1:12" ht="85" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -7293,7 +7369,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -7310,7 +7386,7 @@
     </row>
     <row r="2" spans="1:13" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -7333,34 +7409,34 @@
         <v>244</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>150</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>4</v>
@@ -7374,16 +7450,16 @@
         <v>245</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="G4" s="5">
         <v>1245</v>
@@ -7411,16 +7487,16 @@
         <v>246</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G5" s="12">
         <v>708</v>
@@ -7439,7 +7515,7 @@
         <v>30</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -7450,16 +7526,16 @@
         <v>247</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G6" s="5">
         <v>708</v>
@@ -7487,16 +7563,16 @@
         <v>246</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G7" s="12">
         <v>572.70000000000005</v>
@@ -7515,7 +7591,7 @@
         <v>23</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="25" x14ac:dyDescent="0.35">
@@ -7526,16 +7602,16 @@
         <v>247</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G8" s="5">
         <v>396</v>
@@ -7554,7 +7630,7 @@
         <v>30</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -7565,16 +7641,16 @@
         <v>248</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G9" s="12">
         <v>123</v>
@@ -7593,7 +7669,7 @@
         <v>30</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -7620,7 +7696,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -7637,7 +7713,7 @@
     </row>
     <row r="2" spans="1:13" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -7660,37 +7736,37 @@
         <v>244</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -7701,13 +7777,13 @@
         <v>245</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F4" s="5">
         <v>22340</v>
@@ -7722,13 +7798,13 @@
         <v>18.170000000000002</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="K4" s="5">
         <v>310</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="M4" s="5">
         <v>477.65</v>
@@ -7742,13 +7818,13 @@
         <v>247</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F5" s="12">
         <v>4750</v>
@@ -7763,13 +7839,13 @@
         <v>10.95</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="K5" s="12">
         <v>2400</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="M5" s="12">
         <v>98.37</v>
@@ -7783,13 +7859,13 @@
         <v>246</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F6" s="5">
         <v>662</v>
@@ -7804,13 +7880,13 @@
         <v>8.76</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="K6" s="5">
         <v>12</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="M6" s="5">
         <v>13.54</v>
@@ -7895,7 +7971,7 @@
         <v>36</v>
       </c>
       <c r="B4" s="5">
-        <v>461.14850000000001</v>
+        <v>467.75749999999999</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -7903,11 +7979,11 @@
         <v>37</v>
       </c>
       <c r="F4" s="5">
-        <v>625.02160000000003</v>
+        <v>631.63060000000007</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="5">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4" t="s">
@@ -7919,7 +7995,7 @@
         <v>39</v>
       </c>
       <c r="B5" s="12">
-        <v>455.50380000000001</v>
+        <v>462.11279999999999</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -7927,11 +8003,11 @@
         <v>40</v>
       </c>
       <c r="F5" s="12">
-        <v>625.58620000000008</v>
+        <v>632.19520000000011</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="12">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -7941,7 +8017,7 @@
         <v>41</v>
       </c>
       <c r="B6" s="5">
-        <v>563.57100000000003</v>
+        <v>570.17999999999995</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -7949,11 +8025,11 @@
         <v>42</v>
       </c>
       <c r="F6" s="5">
-        <v>522.5200000000001</v>
+        <v>529.12900000000013</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="5">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -7963,7 +8039,7 @@
         <v>43</v>
       </c>
       <c r="B7" s="12">
-        <v>550.92129999999997</v>
+        <v>557.53030000000001</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -7971,11 +8047,11 @@
         <v>44</v>
       </c>
       <c r="F7" s="12">
-        <v>522.9393</v>
+        <v>529.54830000000004</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="12">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -7985,7 +8061,7 @@
         <v>45</v>
       </c>
       <c r="B8" s="5">
-        <v>556.50670000000002</v>
+        <v>563.11569999999995</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -7993,11 +8069,11 @@
         <v>46</v>
       </c>
       <c r="F8" s="5">
-        <v>634.13270000000011</v>
+        <v>640.74170000000004</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="5">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
@@ -8007,7 +8083,7 @@
         <v>47</v>
       </c>
       <c r="B9" s="12">
-        <v>543.50699999999995</v>
+        <v>550.11599999999999</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -8015,11 +8091,11 @@
         <v>48</v>
       </c>
       <c r="F9" s="12">
-        <v>627.79370000000006</v>
+        <v>634.4027000000001</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="12">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -8029,7 +8105,7 @@
         <v>49</v>
       </c>
       <c r="B10" s="5">
-        <v>554.72490000000005</v>
+        <v>561.33389999999997</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -8037,11 +8113,11 @@
         <v>50</v>
       </c>
       <c r="F10" s="5">
-        <v>633.00520000000006</v>
+        <v>639.61419999999998</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="5">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -8051,7 +8127,7 @@
         <v>51</v>
       </c>
       <c r="B11" s="12">
-        <v>463.85899999999998</v>
+        <v>470.46800000000002</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -8059,11 +8135,11 @@
         <v>52</v>
       </c>
       <c r="F11" s="12">
-        <v>630.03070000000002</v>
+        <v>636.63970000000006</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="12">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -8073,7 +8149,7 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>453.40100000000001</v>
+        <v>460.01</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -8081,11 +8157,11 @@
         <v>54</v>
       </c>
       <c r="F12" s="5">
-        <v>631.37400000000002</v>
+        <v>637.98300000000006</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="5">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -8095,7 +8171,7 @@
         <v>55</v>
       </c>
       <c r="B13" s="12">
-        <v>555.22130000000004</v>
+        <v>561.83029999999997</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -8103,11 +8179,11 @@
         <v>56</v>
       </c>
       <c r="F13" s="12">
-        <v>533.1069</v>
+        <v>539.71590000000003</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="12">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -8117,7 +8193,7 @@
         <v>57</v>
       </c>
       <c r="B14" s="5">
-        <v>551.94960000000003</v>
+        <v>558.55859999999996</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -8125,11 +8201,11 @@
         <v>58</v>
       </c>
       <c r="F14" s="5">
-        <v>521.82230000000004</v>
+        <v>528.43130000000008</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="5">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
@@ -8139,7 +8215,7 @@
         <v>59</v>
       </c>
       <c r="B15" s="12">
-        <v>553.93650000000002</v>
+        <v>560.54550000000006</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -8147,11 +8223,11 @@
         <v>60</v>
       </c>
       <c r="F15" s="12">
-        <v>636.70240000000013</v>
+        <v>643.31140000000005</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="12">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -8161,7 +8237,7 @@
         <v>61</v>
       </c>
       <c r="B16" s="5">
-        <v>545.68809999999996</v>
+        <v>552.2971</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -8169,11 +8245,11 @@
         <v>62</v>
       </c>
       <c r="F16" s="5">
-        <v>639.46900000000005</v>
+        <v>646.07799999999997</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="5">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
@@ -8183,7 +8259,7 @@
         <v>63</v>
       </c>
       <c r="B17" s="12">
-        <v>559.62130000000002</v>
+        <v>566.23029999999994</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -8191,11 +8267,11 @@
         <v>64</v>
       </c>
       <c r="F17" s="12">
-        <v>635.03280000000007</v>
+        <v>641.64179999999999</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="12">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -8205,7 +8281,7 @@
         <v>65</v>
       </c>
       <c r="B18" s="5">
-        <v>456.20760000000001</v>
+        <v>462.81659999999999</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -8213,11 +8289,11 @@
         <v>66</v>
       </c>
       <c r="F18" s="5">
-        <v>643.47460000000001</v>
+        <v>650.08360000000005</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="5">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
@@ -8227,7 +8303,7 @@
         <v>67</v>
       </c>
       <c r="B19" s="12">
-        <v>464.64600000000002</v>
+        <v>471.255</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -8235,11 +8311,11 @@
         <v>68</v>
       </c>
       <c r="F19" s="12">
-        <v>636.91560000000004</v>
+        <v>643.52460000000008</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="12">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -8249,7 +8325,7 @@
         <v>69</v>
       </c>
       <c r="B20" s="5">
-        <v>563.87400000000002</v>
+        <v>570.48299999999995</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -8257,11 +8333,11 @@
         <v>70</v>
       </c>
       <c r="F20" s="5">
-        <v>524.8886</v>
+        <v>531.49760000000003</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="5">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
@@ -8271,7 +8347,7 @@
         <v>71</v>
       </c>
       <c r="B21" s="12">
-        <v>546.76220000000001</v>
+        <v>553.37120000000004</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -8279,11 +8355,11 @@
         <v>72</v>
       </c>
       <c r="F21" s="12">
-        <v>529.5489</v>
+        <v>536.15790000000004</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="12">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
@@ -8295,7 +8371,7 @@
         <v>74</v>
       </c>
       <c r="B22" s="5">
-        <v>544.72749999999996</v>
+        <v>551.3365</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -8303,11 +8379,11 @@
         <v>75</v>
       </c>
       <c r="F22" s="5">
-        <v>627.92690000000005</v>
+        <v>634.53590000000008</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="5">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
@@ -8317,7 +8393,7 @@
         <v>76</v>
       </c>
       <c r="B23" s="12">
-        <v>555.17280000000005</v>
+        <v>561.78179999999998</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -8325,11 +8401,11 @@
         <v>77</v>
       </c>
       <c r="F23" s="12">
-        <v>642.00540000000001</v>
+        <v>648.61440000000005</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="12">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -8339,7 +8415,7 @@
         <v>78</v>
       </c>
       <c r="B24" s="5">
-        <v>555.51290000000006</v>
+        <v>562.12189999999998</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -8347,11 +8423,11 @@
         <v>79</v>
       </c>
       <c r="F24" s="5">
-        <v>628.89940000000001</v>
+        <v>635.50840000000005</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="5">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
@@ -8361,7 +8437,7 @@
         <v>80</v>
       </c>
       <c r="B25" s="12">
-        <v>456.7817</v>
+        <v>463.39069999999998</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -8369,11 +8445,11 @@
         <v>81</v>
       </c>
       <c r="F25" s="12">
-        <v>629.02320000000009</v>
+        <v>635.63220000000001</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="12">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -8383,7 +8459,7 @@
         <v>82</v>
       </c>
       <c r="B26" s="5">
-        <v>452.0933</v>
+        <v>458.70229999999998</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -8391,11 +8467,11 @@
         <v>83</v>
       </c>
       <c r="F26" s="5">
-        <v>644.95950000000005</v>
+        <v>651.56850000000009</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="5">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
@@ -8405,7 +8481,7 @@
         <v>84</v>
       </c>
       <c r="B27" s="12">
-        <v>555.11469999999997</v>
+        <v>561.72370000000001</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -8413,11 +8489,11 @@
         <v>85</v>
       </c>
       <c r="F27" s="12">
-        <v>532.54500000000007</v>
+        <v>539.154</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="12">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
@@ -8427,7 +8503,7 @@
         <v>86</v>
       </c>
       <c r="B28" s="5">
-        <v>558.48099999999999</v>
+        <v>565.09</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -8435,11 +8511,11 @@
         <v>87</v>
       </c>
       <c r="F28" s="5">
-        <v>535.88990000000013</v>
+        <v>542.49890000000005</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="5">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
@@ -8449,7 +8525,7 @@
         <v>88</v>
       </c>
       <c r="B29" s="12">
-        <v>553.61919999999998</v>
+        <v>560.22820000000002</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -8457,11 +8533,11 @@
         <v>89</v>
       </c>
       <c r="F29" s="12">
-        <v>631.09440000000006</v>
+        <v>637.7034000000001</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="12">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
@@ -8471,7 +8547,7 @@
         <v>90</v>
       </c>
       <c r="B30" s="5">
-        <v>551.22130000000004</v>
+        <v>557.83029999999997</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
@@ -8480,10 +8556,10 @@
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="5">
-        <v>606.34525700000006</v>
+        <v>612.9542570000001</v>
       </c>
       <c r="H30" s="5">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -8493,7 +8569,7 @@
         <v>92</v>
       </c>
       <c r="B31" s="12">
-        <v>545.29280000000006</v>
+        <v>551.90179999999998</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -8502,10 +8578,10 @@
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="12">
-        <v>606.34525700000006</v>
+        <v>612.9542570000001</v>
       </c>
       <c r="H31" s="12">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -8515,7 +8591,7 @@
         <v>94</v>
       </c>
       <c r="B32" s="5">
-        <v>460.24250000000001</v>
+        <v>466.85149999999999</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -8524,10 +8600,10 @@
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="5">
-        <v>606.34525700000006</v>
+        <v>612.9542570000001</v>
       </c>
       <c r="H32" s="5">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
@@ -8537,7 +8613,7 @@
         <v>96</v>
       </c>
       <c r="B33" s="12">
-        <v>462.1037</v>
+        <v>468.71269999999998</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -8546,10 +8622,10 @@
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="12">
-        <v>606.34525700000006</v>
+        <v>612.9542570000001</v>
       </c>
       <c r="H33" s="12">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
@@ -8559,7 +8635,7 @@
         <v>98</v>
       </c>
       <c r="B34" s="5">
-        <v>544.94809999999995</v>
+        <v>551.55709999999999</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -8568,10 +8644,10 @@
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="5">
-        <v>424.44168000000002</v>
+        <v>429.06797999999998</v>
       </c>
       <c r="H34" s="5">
-        <v>578.36475000000007</v>
+        <v>584.97375</v>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
@@ -8582,7 +8658,7 @@
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="12">
-        <v>553.49680000000001</v>
+        <v>560.10580000000004</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -8598,7 +8674,7 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="5">
-        <v>559.88810000000001</v>
+        <v>566.49710000000005</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -8614,7 +8690,7 @@
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="12">
-        <v>555.70730000000003</v>
+        <v>562.31629999999996</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -8630,7 +8706,7 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="5">
-        <v>571.92809999999997</v>
+        <v>578.53710000000001</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -8648,7 +8724,7 @@
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="12">
-        <v>459.32940000000002</v>
+        <v>465.9384</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -8664,7 +8740,7 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="5">
-        <v>466.36869999999999</v>
+        <v>472.97770000000003</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -8680,7 +8756,7 @@
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="12">
-        <v>565.64239999999995</v>
+        <v>572.25139999999999</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
@@ -8696,7 +8772,7 @@
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="5">
-        <v>586.09050000000002</v>
+        <v>592.69950000000006</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -8712,7 +8788,7 @@
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="12">
-        <v>597.45690000000002</v>
+        <v>604.06590000000006</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -8728,7 +8804,7 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="5">
-        <v>598.43500000000006</v>
+        <v>605.04399999999998</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -8744,7 +8820,7 @@
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="12">
-        <v>592.74289999999996</v>
+        <v>599.3519</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -8760,7 +8836,7 @@
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="5">
-        <v>497.28289999999998</v>
+        <v>503.89190000000002</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -8776,7 +8852,7 @@
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="12">
-        <v>502.35759999999999</v>
+        <v>508.96660000000003</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
@@ -8792,7 +8868,7 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5">
-        <v>599.6875</v>
+        <v>606.29650000000004</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -8808,7 +8884,7 @@
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="12">
-        <v>636.48860000000002</v>
+        <v>643.09760000000006</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -8824,7 +8900,7 @@
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="5">
-        <v>617.72800000000007</v>
+        <v>624.33699999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -8840,7 +8916,7 @@
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="12">
-        <v>631.40219999999999</v>
+        <v>638.01120000000003</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
@@ -8856,7 +8932,7 @@
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="5">
-        <v>632.36149999999998</v>
+        <v>638.97050000000002</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -8872,7 +8948,7 @@
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="12">
-        <v>524.0258</v>
+        <v>530.63480000000004</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
@@ -8888,7 +8964,7 @@
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="5">
-        <v>520.97580000000005</v>
+        <v>527.58479999999997</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -8904,7 +8980,7 @@
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="12">
-        <v>621.6232</v>
+        <v>628.23220000000003</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
@@ -8922,7 +8998,7 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="5">
-        <v>619.85619999999994</v>
+        <v>626.46519999999998</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -8938,7 +9014,7 @@
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="12">
-        <v>628.68520000000001</v>
+        <v>635.29420000000005</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
@@ -8954,7 +9030,7 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="5">
-        <v>627.81989999999996</v>
+        <v>634.4289</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -8970,7 +9046,7 @@
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="12">
-        <v>640.27930000000003</v>
+        <v>646.88829999999996</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
@@ -8986,7 +9062,7 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="5">
-        <v>522.6558</v>
+        <v>529.26480000000004</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -9002,7 +9078,7 @@
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="12">
-        <v>525.76089999999999</v>
+        <v>532.36990000000003</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
@@ -9018,7 +9094,7 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="5">
-        <v>637.30960000000005</v>
+        <v>643.91859999999997</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -9034,7 +9110,7 @@
       </c>
       <c r="B63" s="2"/>
       <c r="C63" s="12">
-        <v>622.77660000000003</v>
+        <v>629.38560000000007</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
@@ -9050,7 +9126,7 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="5">
-        <v>634.77980000000002</v>
+        <v>641.38880000000006</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -9107,10 +9183,10 @@
         <v>133</v>
       </c>
       <c r="B68" s="5">
-        <v>9893.9446000000007</v>
+        <v>10098.8236</v>
       </c>
       <c r="C68" s="5">
-        <v>9986.268</v>
+        <v>10184.538</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -9269,7 +9345,7 @@
         <v>143</v>
       </c>
       <c r="B78" s="5">
-        <v>71.957000000000107</v>
+        <v>71.299999999999955</v>
       </c>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -9317,7 +9393,7 @@
         <v>146</v>
       </c>
       <c r="B81" s="12">
-        <v>-25.199999999999822</v>
+        <v>-31.15200000000004</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
@@ -9421,7 +9497,7 @@
         <v>151</v>
       </c>
       <c r="B88" s="5">
-        <v>616.38940000000002</v>
+        <v>609.78039999999964</v>
       </c>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
@@ -9472,7 +9548,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -9484,7 +9560,7 @@
     </row>
     <row r="2" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -9499,25 +9575,25 @@
         <v>154</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="25" x14ac:dyDescent="0.35">
@@ -9525,7 +9601,7 @@
         <v>159</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C4" s="5">
         <v>3556.31</v>
@@ -9534,16 +9610,16 @@
         <v>1290</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="F4" s="5">
         <v>30</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25" x14ac:dyDescent="0.35">
@@ -9551,7 +9627,7 @@
         <v>162</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C5" s="12">
         <v>1815.53</v>
@@ -9560,16 +9636,16 @@
         <v>560</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="F5" s="12">
         <v>30</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>
@@ -9594,7 +9670,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -9607,7 +9683,7 @@
     </row>
     <row r="2" spans="1:9" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -9623,25 +9699,25 @@
         <v>154</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>4</v>
@@ -9652,28 +9728,28 @@
         <v>159</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="C4" s="5">
         <v>15000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="H4" s="5">
         <v>11840</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
@@ -9698,13 +9774,13 @@
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="B1" s="17"/>
     </row>
     <row r="2" spans="1:2" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B2" s="18"/>
     </row>
@@ -9718,210 +9794,210 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="25" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="25" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="25" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="25" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="25" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
     </row>
   </sheetData>
@@ -10030,33 +10106,33 @@
         <v>159</v>
       </c>
       <c r="C4" s="5">
-        <v>9429.7855999999992</v>
+        <v>9634.6646000000001</v>
       </c>
       <c r="D4" s="5">
-        <v>9664.9979999999996</v>
+        <v>9863.268</v>
       </c>
       <c r="E4" s="10">
         <f>D4-C4</f>
-        <v>235.21240000000034</v>
+        <v>228.60339999999997</v>
       </c>
       <c r="F4" s="9">
         <f>D4/C4-1</f>
-        <v>2.4943557571446728E-2</v>
+        <v>2.3727177799214738E-2</v>
       </c>
       <c r="G4" s="10">
         <f>C4/31</f>
-        <v>304.18663225806449</v>
+        <v>310.79563225806453</v>
       </c>
       <c r="H4" s="10">
         <f>D4/30</f>
-        <v>322.16659999999996</v>
+        <v>328.7756</v>
       </c>
       <c r="I4" s="9">
         <f>H4/G4-1</f>
-        <v>5.9108342823828375E-2</v>
+        <v>5.7851417059188392E-2</v>
       </c>
       <c r="J4" s="5">
-        <v>9664.9979999999996</v>
+        <v>9863.268</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>160</v>
@@ -10352,30 +10428,30 @@
         <v>133</v>
       </c>
       <c r="B4" s="5">
-        <v>9893.9446000000007</v>
+        <v>10098.8236</v>
       </c>
       <c r="C4" s="5">
-        <v>9986.268</v>
+        <v>10184.538</v>
       </c>
       <c r="D4" s="10">
         <f>C4-B4</f>
-        <v>92.32339999999931</v>
+        <v>85.714400000000751</v>
       </c>
       <c r="E4" s="9">
         <f>C4/B4-1</f>
-        <v>9.3313035126554311E-3</v>
+        <v>8.4875628484095689E-3</v>
       </c>
       <c r="F4" s="10">
         <f>B4/31</f>
-        <v>319.15950322580647</v>
+        <v>325.76850322580646</v>
       </c>
       <c r="G4" s="10">
         <f>C4/30</f>
-        <v>332.87560000000002</v>
+        <v>339.4846</v>
       </c>
       <c r="H4" s="9">
         <f>G4/F4-1</f>
-        <v>4.2975680296410745E-2</v>
+        <v>4.2103814943356355E-2</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -10608,30 +10684,30 @@
         <v>146</v>
       </c>
       <c r="B6" s="5">
-        <v>2638.2240000000002</v>
+        <v>2822.7359999999999</v>
       </c>
       <c r="C6" s="5">
-        <v>2613.0239999999999</v>
+        <v>2791.5839999999998</v>
       </c>
       <c r="D6" s="10">
         <f t="shared" si="0"/>
-        <v>-25.200000000000273</v>
+        <v>-31.152000000000044</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="1"/>
-        <v>-9.5518803558758414E-3</v>
+        <v>-1.1036101144421551E-2</v>
       </c>
       <c r="F6" s="10">
         <f t="shared" si="2"/>
-        <v>85.103999999999999</v>
+        <v>91.055999999999997</v>
       </c>
       <c r="G6" s="10">
         <f t="shared" si="3"/>
-        <v>87.100799999999992</v>
+        <v>93.052799999999991</v>
       </c>
       <c r="H6" s="9">
         <f t="shared" si="4"/>
-        <v>2.3463056965594919E-2</v>
+        <v>2.1929362150764353E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -10732,30 +10808,30 @@
         <v>143</v>
       </c>
       <c r="B10" s="5">
-        <v>727.19399999999996</v>
+        <v>747.56100000000004</v>
       </c>
       <c r="C10" s="5">
-        <v>799.15100000000007</v>
+        <v>818.86099999999999</v>
       </c>
       <c r="D10" s="10">
         <f t="shared" si="0"/>
-        <v>71.957000000000107</v>
+        <v>71.299999999999955</v>
       </c>
       <c r="E10" s="9">
         <f t="shared" si="1"/>
-        <v>9.8951586509239853E-2</v>
+        <v>9.5376832124736133E-2</v>
       </c>
       <c r="F10" s="10">
         <f t="shared" si="2"/>
-        <v>23.457870967741933</v>
+        <v>24.114870967741936</v>
       </c>
       <c r="G10" s="10">
         <f t="shared" si="3"/>
-        <v>26.63836666666667</v>
+        <v>27.295366666666666</v>
       </c>
       <c r="H10" s="9">
         <f t="shared" si="4"/>
-        <v>0.13558330605954794</v>
+        <v>0.1318893931955607</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -10993,30 +11069,30 @@
         <v>182</v>
       </c>
       <c r="B4" s="5">
-        <v>11438.662200000001</v>
+        <v>11643.5412</v>
       </c>
       <c r="C4" s="5">
-        <v>12055.051600000001</v>
+        <v>12253.321599999999</v>
       </c>
       <c r="D4" s="10">
         <f>C4-B4</f>
-        <v>616.38940000000002</v>
+        <v>609.78039999999964</v>
       </c>
       <c r="E4" s="9">
         <f>C4/C6</f>
-        <v>0.69477791192034666</v>
+        <v>0.69822629362998467</v>
       </c>
       <c r="F4" s="10">
         <f>B4/31</f>
-        <v>368.98910322580645</v>
+        <v>375.59810322580643</v>
       </c>
       <c r="G4" s="10">
         <f>C4/30</f>
-        <v>401.83505333333335</v>
+        <v>408.44405333333333</v>
       </c>
       <c r="H4" s="9">
         <f>G4/F4-1</f>
-        <v>8.901604361857407E-2</v>
+        <v>8.7449723056189699E-2</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>183</v>
@@ -11038,7 +11114,7 @@
       </c>
       <c r="E5" s="11">
         <f>C5/C6</f>
-        <v>0.30522208807965329</v>
+        <v>0.30177370637001516</v>
       </c>
       <c r="F5" s="8">
         <f>B5/31</f>
@@ -11062,15 +11138,15 @@
       </c>
       <c r="B6" s="10">
         <f>SUM(B4:B5)</f>
-        <v>16196.3613</v>
+        <v>16401.240299999998</v>
       </c>
       <c r="C6" s="10">
         <f>SUM(C4:C5)</f>
-        <v>17350.942500000001</v>
+        <v>17549.212500000001</v>
       </c>
       <c r="D6" s="10">
         <f>C6-B6</f>
-        <v>1154.5812000000005</v>
+        <v>1147.9722000000038</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="4"/>
@@ -11379,14 +11455,14 @@
         <v>143</v>
       </c>
       <c r="C9" s="12">
-        <v>212.73439999999999</v>
+        <v>233.10140000000001</v>
       </c>
       <c r="D9" s="12">
-        <v>216.63239999999999</v>
+        <v>236.3424</v>
       </c>
       <c r="E9" s="8">
         <f t="shared" si="0"/>
-        <v>3.8979999999999961</v>
+        <v>3.2409999999999854</v>
       </c>
       <c r="F9" s="12">
         <v>0</v>
@@ -11395,17 +11471,17 @@
         <v>0</v>
       </c>
       <c r="H9" s="12">
-        <v>10.760438148399411</v>
+        <v>10.760444506465969</v>
       </c>
       <c r="I9" s="12">
-        <v>-6.8624000000000107</v>
+        <v>-7.5194000000000134</v>
       </c>
       <c r="J9" s="12">
-        <v>-3.8148399404747117E-5</v>
+        <v>-4.4506465972204978E-5</v>
       </c>
       <c r="K9" s="8">
         <f t="shared" si="1"/>
-        <v>3.8979999999999952</v>
+        <v>3.2409999999999837</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>202</v>
@@ -11459,14 +11535,14 @@
         <v>146</v>
       </c>
       <c r="C11" s="12">
-        <v>1590.672</v>
+        <v>1775.184</v>
       </c>
       <c r="D11" s="12">
-        <v>1539.36</v>
+        <v>1717.92</v>
       </c>
       <c r="E11" s="8">
         <f t="shared" si="0"/>
-        <v>-51.312000000000126</v>
+        <v>-57.263999999999896</v>
       </c>
       <c r="F11" s="12">
         <v>0</v>
@@ -11478,14 +11554,14 @@
         <v>0</v>
       </c>
       <c r="I11" s="12">
-        <v>-51.311999999999998</v>
+        <v>-57.264000000000003</v>
       </c>
       <c r="J11" s="12">
         <v>0</v>
       </c>
       <c r="K11" s="8">
         <f t="shared" si="1"/>
-        <v>-51.311999999999998</v>
+        <v>-57.264000000000003</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>204</v>
@@ -11989,16 +12065,16 @@
         <v>234</v>
       </c>
       <c r="F12" s="5">
-        <v>122.202</v>
+        <v>142.56899999999999</v>
       </c>
       <c r="G12" s="5">
-        <v>118.26</v>
+        <v>137.97</v>
       </c>
       <c r="H12" s="5">
-        <v>6.1999979999999999</v>
+        <v>7.2333309999999997</v>
       </c>
       <c r="I12" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J12" s="5">
         <v>19.710006358066568</v>
@@ -12059,16 +12135,16 @@
         <v>219</v>
       </c>
       <c r="F14" s="5">
-        <v>738.048</v>
+        <v>922.56</v>
       </c>
       <c r="G14" s="5">
-        <v>714.24</v>
+        <v>892.8</v>
       </c>
       <c r="H14" s="5">
-        <v>2976</v>
+        <v>3720</v>
       </c>
       <c r="I14" s="5">
-        <v>2880</v>
+        <v>3600</v>
       </c>
       <c r="J14" s="5">
         <v>0.248</v>
@@ -12491,14 +12567,14 @@
         <v>146</v>
       </c>
       <c r="D10" s="5">
-        <v>1590.672</v>
+        <v>1775.184</v>
       </c>
       <c r="E10" s="5">
-        <v>1539.36</v>
+        <v>1717.92</v>
       </c>
       <c r="F10" s="10">
         <f t="shared" si="0"/>
-        <v>-51.312000000000126</v>
+        <v>-57.263999999999896</v>
       </c>
       <c r="G10" s="14">
         <v>-3.2258064516129108E-2</v>
@@ -12815,20 +12891,20 @@
         <v>143</v>
       </c>
       <c r="D22" s="5">
-        <v>212.73439999999999</v>
+        <v>233.10140000000001</v>
       </c>
       <c r="E22" s="5">
-        <v>216.63239999999999</v>
+        <v>236.3424</v>
       </c>
       <c r="F22" s="10">
         <f t="shared" si="0"/>
-        <v>3.8979999999999961</v>
+        <v>3.2409999999999854</v>
       </c>
       <c r="G22" s="14">
-        <v>1.8323317714483481E-2</v>
+        <v>1.3903820397475061E-2</v>
       </c>
       <c r="H22" s="14">
-        <v>5.2267428304966217E-2</v>
+        <v>4.7700614410724151E-2</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
